--- a/AAII_Financials/Quarterly/PMCB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PMCB_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
   <si>
     <t>PMCB</t>
   </si>
@@ -656,136 +656,140 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44043</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43951</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43861</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43769</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43677</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43585</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43496</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43404</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43312</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43220</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43131</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43039</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42947</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42855</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42766</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -873,8 +877,11 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -962,8 +969,11 @@
       <c r="AE9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1051,8 +1061,11 @@
       <c r="AE10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1096,85 +1110,88 @@
         <v>100</v>
       </c>
       <c r="F12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H12" s="3">
         <v>200</v>
       </c>
       <c r="I12" s="3">
+        <v>200</v>
+      </c>
+      <c r="J12" s="3">
         <v>300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>200</v>
-      </c>
-      <c r="K12" s="3">
-        <v>100</v>
       </c>
       <c r="L12" s="3">
         <v>100</v>
       </c>
       <c r="M12" s="3">
+        <v>100</v>
+      </c>
+      <c r="N12" s="3">
         <v>300</v>
-      </c>
-      <c r="N12" s="3">
-        <v>200</v>
       </c>
       <c r="O12" s="3">
         <v>200</v>
       </c>
       <c r="P12" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q12" s="3">
         <v>300</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>100</v>
       </c>
       <c r="R12" s="3">
         <v>100</v>
       </c>
       <c r="S12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T12" s="3">
+        <v>0</v>
+      </c>
+      <c r="U12" s="3">
         <v>100</v>
       </c>
-      <c r="U12" s="3">
-        <v>0</v>
-      </c>
       <c r="V12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W12" s="3">
         <v>100</v>
       </c>
       <c r="X12" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Y12" s="3">
         <v>300</v>
       </c>
       <c r="Z12" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA12" s="3">
         <v>800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1282,11 +1302,11 @@
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
@@ -1294,12 +1314,12 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3">
         <v>-100</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1315,8 +1335,8 @@
       <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1351,8 +1371,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,34 +1496,35 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E17" s="3">
         <v>2100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>900</v>
-      </c>
-      <c r="K17" s="3">
-        <v>1000</v>
       </c>
       <c r="L17" s="3">
         <v>1000</v>
@@ -1506,61 +1533,64 @@
         <v>1000</v>
       </c>
       <c r="N17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O17" s="3">
         <v>800</v>
-      </c>
-      <c r="O17" s="3">
-        <v>900</v>
       </c>
       <c r="P17" s="3">
         <v>900</v>
       </c>
       <c r="Q17" s="3">
+        <v>900</v>
+      </c>
+      <c r="R17" s="3">
         <v>700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>900</v>
-      </c>
-      <c r="S17" s="3">
-        <v>1100</v>
       </c>
       <c r="T17" s="3">
         <v>1100</v>
       </c>
       <c r="U17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V17" s="3">
         <v>1200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1568,25 +1598,25 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-900</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-1000</v>
       </c>
       <c r="L18" s="3">
         <v>-1000</v>
@@ -1595,61 +1625,64 @@
         <v>-1000</v>
       </c>
       <c r="N18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="O18" s="3">
         <v>-800</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-900</v>
       </c>
       <c r="P18" s="3">
         <v>-900</v>
       </c>
       <c r="Q18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="R18" s="3">
         <v>-700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-900</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-1100</v>
       </c>
       <c r="T18" s="3">
         <v>-1100</v>
       </c>
       <c r="U18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="V18" s="3">
         <v>-1200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,8 +1714,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1690,22 +1724,22 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>800</v>
+        <v>-1100</v>
       </c>
       <c r="F20" s="3">
         <v>800</v>
       </c>
       <c r="G20" s="3">
+        <v>800</v>
+      </c>
+      <c r="H20" s="3">
         <v>400</v>
-      </c>
-      <c r="H20" s="3">
-        <v>100</v>
       </c>
       <c r="I20" s="3">
         <v>100</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1750,11 +1784,11 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
@@ -1770,8 +1804,11 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1779,26 +1816,26 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-800</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1859,16 +1896,19 @@
       <c r="AE21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1906,8 +1946,8 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>4</v>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>4</v>
@@ -1927,8 +1967,8 @@
       <c r="X22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="Y22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
@@ -1948,34 +1988,37 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-800</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-1000</v>
       </c>
       <c r="L23" s="3">
         <v>-1000</v>
@@ -1984,22 +2027,22 @@
         <v>-1000</v>
       </c>
       <c r="N23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="O23" s="3">
         <v>-800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-900</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-1100</v>
       </c>
       <c r="T23" s="3">
         <v>-1100</v>
@@ -2008,37 +2051,40 @@
         <v>-1100</v>
       </c>
       <c r="V23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="W23" s="3">
         <v>-700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2126,8 +2172,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,34 +2264,37 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-800</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-1000</v>
       </c>
       <c r="L26" s="3">
         <v>-1000</v>
@@ -2251,22 +2303,22 @@
         <v>-1000</v>
       </c>
       <c r="N26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="O26" s="3">
         <v>-800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-900</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-1100</v>
       </c>
       <c r="T26" s="3">
         <v>-1100</v>
@@ -2275,63 +2327,66 @@
         <v>-1100</v>
       </c>
       <c r="V26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="W26" s="3">
         <v>-700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-3500</v>
+        <v>-2300</v>
       </c>
       <c r="E27" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="F27" s="3">
         <v>-100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-800</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-1000</v>
       </c>
       <c r="L27" s="3">
         <v>-1000</v>
@@ -2340,22 +2395,22 @@
         <v>-1000</v>
       </c>
       <c r="N27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="O27" s="3">
         <v>-800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-900</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-1100</v>
       </c>
       <c r="T27" s="3">
         <v>-1100</v>
@@ -2364,37 +2419,40 @@
         <v>-1100</v>
       </c>
       <c r="V27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="W27" s="3">
         <v>-700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2816,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2758,22 +2828,22 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>-800</v>
+        <v>1100</v>
       </c>
       <c r="F32" s="3">
         <v>-800</v>
       </c>
       <c r="G32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H32" s="3">
         <v>-400</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-100</v>
       </c>
       <c r="I32" s="3">
         <v>-100</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2818,11 +2888,11 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
@@ -2838,34 +2908,37 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-3500</v>
+        <v>-2300</v>
       </c>
       <c r="E33" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="F33" s="3">
         <v>-100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-800</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-1000</v>
       </c>
       <c r="L33" s="3">
         <v>-1000</v>
@@ -2874,22 +2947,22 @@
         <v>-1000</v>
       </c>
       <c r="N33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="O33" s="3">
         <v>-800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-900</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-1100</v>
       </c>
       <c r="T33" s="3">
         <v>-1100</v>
@@ -2898,37 +2971,40 @@
         <v>-1100</v>
       </c>
       <c r="V33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="W33" s="3">
         <v>-700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,34 +3092,37 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-3500</v>
+        <v>-2300</v>
       </c>
       <c r="E35" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="F35" s="3">
         <v>-100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-800</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-1000</v>
       </c>
       <c r="L35" s="3">
         <v>-1000</v>
@@ -3052,22 +3131,22 @@
         <v>-1000</v>
       </c>
       <c r="N35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="O35" s="3">
         <v>-800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-900</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-1100</v>
       </c>
       <c r="T35" s="3">
         <v>-1100</v>
@@ -3076,131 +3155,137 @@
         <v>-1100</v>
       </c>
       <c r="V35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="W35" s="3">
         <v>-700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44043</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43951</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43861</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43769</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43677</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43585</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43496</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43404</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43312</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43220</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43131</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43039</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42947</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42855</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42766</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,97 +3351,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>73400</v>
+      </c>
+      <c r="E41" s="3">
         <v>74700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>68000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>72600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>77000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>82200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>85400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>86600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>86900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>100</v>
       </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
       <c r="T41" s="3">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3">
         <v>300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,8 +3533,11 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3532,8 +3625,11 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3621,46 +3717,49 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E45" s="3">
         <v>100</v>
       </c>
       <c r="F45" s="3">
+        <v>100</v>
+      </c>
+      <c r="G45" s="3">
         <v>200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
       <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
         <v>100</v>
-      </c>
-      <c r="J45" s="3">
-        <v>200</v>
       </c>
       <c r="K45" s="3">
         <v>200</v>
       </c>
       <c r="L45" s="3">
+        <v>200</v>
+      </c>
+      <c r="M45" s="3">
         <v>500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
       <c r="O45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P45" s="3">
         <v>100</v>
@@ -3672,28 +3771,28 @@
         <v>100</v>
       </c>
       <c r="S45" s="3">
+        <v>100</v>
+      </c>
+      <c r="T45" s="3">
         <v>200</v>
-      </c>
-      <c r="T45" s="3">
-        <v>100</v>
       </c>
       <c r="U45" s="3">
         <v>100</v>
       </c>
       <c r="V45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
       </c>
       <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
         <v>100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>200</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>100</v>
       </c>
       <c r="AA45" s="3">
         <v>100</v>
@@ -3705,102 +3804,108 @@
         <v>100</v>
       </c>
       <c r="AD45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>73700</v>
+      </c>
+      <c r="E46" s="3">
         <v>74800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>68100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>72800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>77200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>82300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>85500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>86800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>87200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1000</v>
-      </c>
-      <c r="R46" s="3">
-        <v>200</v>
       </c>
       <c r="S46" s="3">
         <v>200</v>
       </c>
       <c r="T46" s="3">
+        <v>200</v>
+      </c>
+      <c r="U46" s="3">
         <v>500</v>
-      </c>
-      <c r="U46" s="3">
-        <v>700</v>
       </c>
       <c r="V46" s="3">
         <v>700</v>
       </c>
       <c r="W46" s="3">
+        <v>700</v>
+      </c>
+      <c r="X46" s="3">
         <v>900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3888,8 +3993,11 @@
       <c r="AE47" s="3">
         <v>1600</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3977,8 +4085,11 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4066,8 +4177,11 @@
       <c r="AE49" s="3">
         <v>3500</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,8 +4361,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4333,8 +4453,11 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4545,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>78900</v>
+      </c>
+      <c r="E54" s="3">
         <v>79900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>73300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>78000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>82300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>87400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>90600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>91900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>92300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6200</v>
-      </c>
-      <c r="R54" s="3">
-        <v>5300</v>
       </c>
       <c r="S54" s="3">
         <v>5300</v>
       </c>
       <c r="T54" s="3">
+        <v>5300</v>
+      </c>
+      <c r="U54" s="3">
         <v>5600</v>
-      </c>
-      <c r="U54" s="3">
-        <v>5800</v>
       </c>
       <c r="V54" s="3">
         <v>5800</v>
       </c>
       <c r="W54" s="3">
+        <v>5800</v>
+      </c>
+      <c r="X54" s="3">
         <v>6100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>9500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>8700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,61 +4707,62 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>100</v>
+      </c>
+      <c r="E57" s="3">
         <v>700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>200</v>
-      </c>
-      <c r="N57" s="3">
-        <v>100</v>
       </c>
       <c r="O57" s="3">
         <v>100</v>
       </c>
       <c r="P57" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q57" s="3">
         <v>400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>200</v>
-      </c>
-      <c r="T57" s="3">
-        <v>100</v>
       </c>
       <c r="U57" s="3">
         <v>100</v>
@@ -4640,34 +4771,37 @@
         <v>100</v>
       </c>
       <c r="W57" s="3">
+        <v>100</v>
+      </c>
+      <c r="X57" s="3">
         <v>300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>400</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>300</v>
       </c>
       <c r="AA57" s="3">
         <v>300</v>
       </c>
       <c r="AB57" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC57" s="3">
         <v>600</v>
-      </c>
-      <c r="AC57" s="3">
-        <v>400</v>
       </c>
       <c r="AD57" s="3">
         <v>400</v>
       </c>
       <c r="AE57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4702,19 +4836,19 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O58" s="3">
         <v>100</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>4</v>
+      <c r="R58" s="3">
+        <v>0</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>4</v>
@@ -4731,8 +4865,8 @@
       <c r="W58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -4755,25 +4889,28 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E59" s="3">
         <v>800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>500</v>
-      </c>
-      <c r="F59" s="3">
-        <v>400</v>
       </c>
       <c r="G59" s="3">
         <v>400</v>
       </c>
       <c r="H59" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I59" s="3">
         <v>500</v>
@@ -4782,40 +4919,40 @@
         <v>500</v>
       </c>
       <c r="K59" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L59" s="3">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3">
         <v>500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>600</v>
-      </c>
-      <c r="N59" s="3">
-        <v>500</v>
       </c>
       <c r="O59" s="3">
         <v>500</v>
       </c>
       <c r="P59" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q59" s="3">
         <v>700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>600</v>
-      </c>
-      <c r="V59" s="3">
-        <v>300</v>
       </c>
       <c r="W59" s="3">
         <v>300</v>
@@ -4827,114 +4964,120 @@
         <v>300</v>
       </c>
       <c r="Z59" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA59" s="3">
         <v>600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>300</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>200</v>
       </c>
       <c r="AC59" s="3">
         <v>200</v>
       </c>
       <c r="AD59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AE59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E60" s="3">
         <v>1500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>700</v>
-      </c>
-      <c r="N60" s="3">
-        <v>600</v>
       </c>
       <c r="O60" s="3">
         <v>600</v>
       </c>
       <c r="P60" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q60" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>1000</v>
       </c>
       <c r="R60" s="3">
         <v>1000</v>
       </c>
       <c r="S60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T60" s="3">
         <v>800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>900</v>
-      </c>
-      <c r="AC60" s="3">
-        <v>600</v>
       </c>
       <c r="AD60" s="3">
         <v>600</v>
       </c>
       <c r="AE60" s="3">
+        <v>600</v>
+      </c>
+      <c r="AF60" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5022,17 +5165,20 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E62" s="3">
         <v>18900</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F62" s="3" t="s">
         <v>4</v>
       </c>
@@ -5048,8 +5194,8 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5533,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E66" s="3">
         <v>20400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>900</v>
-      </c>
-      <c r="AC66" s="3">
-        <v>600</v>
       </c>
       <c r="AD66" s="3">
         <v>600</v>
       </c>
       <c r="AE66" s="3">
+        <v>600</v>
+      </c>
+      <c r="AF66" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,17 +5843,20 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E70" s="3">
         <v>16800</v>
       </c>
-      <c r="E70" s="3">
-        <v>0</v>
-      </c>
       <c r="F70" s="3">
         <v>0</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6027,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-116400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-119500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-116000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-115800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-115100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-113200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-111600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-110200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-109400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-108400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-107400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-106400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-105700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-104700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-103900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-103100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-102200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-101200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-100000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-98900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-98200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-97200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-96000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-94700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-92600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-90800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-89100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-88000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-86700</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>36800</v>
+      </c>
+      <c r="E76" s="3">
         <v>42700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>72700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>77100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>81000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>86300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>89900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>91300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>92100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4500</v>
-      </c>
-      <c r="T76" s="3">
-        <v>5000</v>
       </c>
       <c r="U76" s="3">
         <v>5000</v>
       </c>
       <c r="V76" s="3">
-        <v>5400</v>
+        <v>5000</v>
       </c>
       <c r="W76" s="3">
         <v>5400</v>
       </c>
       <c r="X76" s="3">
+        <v>5400</v>
+      </c>
+      <c r="Y76" s="3">
         <v>6200</v>
-      </c>
-      <c r="Y76" s="3">
-        <v>5800</v>
       </c>
       <c r="Z76" s="3">
         <v>5800</v>
       </c>
       <c r="AA76" s="3">
+        <v>5800</v>
+      </c>
+      <c r="AB76" s="3">
         <v>7300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,128 +6579,134 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44043</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43951</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43861</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43769</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43677</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43585</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43496</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43404</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43312</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43220</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43131</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43039</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42947</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42855</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42766</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-3500</v>
+        <v>-2300</v>
       </c>
       <c r="E81" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="F81" s="3">
         <v>-100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-800</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-1000</v>
       </c>
       <c r="L81" s="3">
         <v>-1000</v>
@@ -6520,22 +6715,22 @@
         <v>-1000</v>
       </c>
       <c r="N81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="O81" s="3">
         <v>-800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-900</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-1100</v>
       </c>
       <c r="T81" s="3">
         <v>-1100</v>
@@ -6544,37 +6739,40 @@
         <v>-1100</v>
       </c>
       <c r="V81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="W81" s="3">
         <v>-700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6695,8 +6894,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E89" s="3">
         <v>300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1300</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-600</v>
       </c>
       <c r="Q89" s="3">
         <v>-600</v>
       </c>
       <c r="R89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="S89" s="3">
         <v>-400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-800</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-700</v>
       </c>
       <c r="V89" s="3">
         <v>-700</v>
       </c>
       <c r="W89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="X89" s="3">
         <v>-900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7482,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7351,8 +7572,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,8 +7756,11 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7618,8 +7848,11 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,85 +8250,88 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>700</v>
+      </c>
+      <c r="E100" s="3">
         <v>6300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>87400</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>2800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>600</v>
-      </c>
-      <c r="U100" s="3">
-        <v>500</v>
       </c>
       <c r="V100" s="3">
         <v>500</v>
       </c>
       <c r="W100" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>1400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>900</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
       <c r="AB100" s="3">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="AC100" s="3">
         <v>1800</v>
@@ -8094,10 +8340,13 @@
         <v>1800</v>
       </c>
       <c r="AE100" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8185,61 +8434,64 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E102" s="3">
         <v>6600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>86000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-300</v>
-      </c>
-      <c r="T102" s="3">
-        <v>-200</v>
       </c>
       <c r="U102" s="3">
         <v>-200</v>
@@ -8248,30 +8500,33 @@
         <v>-200</v>
       </c>
       <c r="W102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="X102" s="3">
         <v>-900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PMCB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PMCB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
   <si>
     <t>PMCB</t>
   </si>
@@ -656,140 +656,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
         <v>45230</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45138</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45046</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44957</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44865</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44773</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44592</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44500</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44316</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44227</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44135</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44043</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43951</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43861</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43769</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43677</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43585</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43496</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43404</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43312</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43220</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43131</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43039</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42947</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42855</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42766</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -880,8 +884,11 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -972,8 +979,11 @@
       <c r="AF9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1064,8 +1074,11 @@
       <c r="AF10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1107,91 +1121,94 @@
         <v>100</v>
       </c>
       <c r="E12" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F12" s="3">
         <v>100</v>
       </c>
       <c r="G12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I12" s="3">
         <v>200</v>
       </c>
       <c r="J12" s="3">
+        <v>200</v>
+      </c>
+      <c r="K12" s="3">
         <v>300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>200</v>
-      </c>
-      <c r="L12" s="3">
-        <v>100</v>
       </c>
       <c r="M12" s="3">
         <v>100</v>
       </c>
       <c r="N12" s="3">
+        <v>100</v>
+      </c>
+      <c r="O12" s="3">
         <v>300</v>
-      </c>
-      <c r="O12" s="3">
-        <v>200</v>
       </c>
       <c r="P12" s="3">
         <v>200</v>
       </c>
       <c r="Q12" s="3">
+        <v>200</v>
+      </c>
+      <c r="R12" s="3">
         <v>300</v>
-      </c>
-      <c r="R12" s="3">
-        <v>100</v>
       </c>
       <c r="S12" s="3">
         <v>100</v>
       </c>
       <c r="T12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U12" s="3">
+        <v>0</v>
+      </c>
+      <c r="V12" s="3">
         <v>100</v>
       </c>
-      <c r="V12" s="3">
-        <v>0</v>
-      </c>
       <c r="W12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X12" s="3">
         <v>100</v>
       </c>
       <c r="Y12" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Z12" s="3">
         <v>300</v>
       </c>
       <c r="AA12" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB12" s="3">
         <v>800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1299,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1305,11 +1325,11 @@
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
@@ -1317,12 +1337,12 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3">
         <v>-100</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1338,8 +1358,8 @@
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1374,8 +1394,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,37 +1523,38 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1400</v>
+        <v>1900</v>
       </c>
       <c r="E17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F17" s="3">
         <v>2100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>900</v>
-      </c>
-      <c r="L17" s="3">
-        <v>1000</v>
       </c>
       <c r="M17" s="3">
         <v>1000</v>
@@ -1536,61 +1563,64 @@
         <v>1000</v>
       </c>
       <c r="O17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P17" s="3">
         <v>800</v>
-      </c>
-      <c r="P17" s="3">
-        <v>900</v>
       </c>
       <c r="Q17" s="3">
         <v>900</v>
       </c>
       <c r="R17" s="3">
+        <v>900</v>
+      </c>
+      <c r="S17" s="3">
         <v>700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>900</v>
-      </c>
-      <c r="T17" s="3">
-        <v>1100</v>
       </c>
       <c r="U17" s="3">
         <v>1100</v>
       </c>
       <c r="V17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W17" s="3">
         <v>1200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1598,28 +1628,28 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-900</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-1000</v>
       </c>
       <c r="M18" s="3">
         <v>-1000</v>
@@ -1628,61 +1658,64 @@
         <v>-1000</v>
       </c>
       <c r="O18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P18" s="3">
         <v>-800</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-900</v>
       </c>
       <c r="Q18" s="3">
         <v>-900</v>
       </c>
       <c r="R18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="S18" s="3">
         <v>-700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-900</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-1100</v>
       </c>
       <c r="U18" s="3">
         <v>-1100</v>
       </c>
       <c r="V18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="W18" s="3">
         <v>-1200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1748,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1724,25 +1758,25 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1100</v>
-      </c>
-      <c r="F20" s="3">
-        <v>800</v>
       </c>
       <c r="G20" s="3">
         <v>800</v>
       </c>
       <c r="H20" s="3">
+        <v>800</v>
+      </c>
+      <c r="I20" s="3">
         <v>400</v>
-      </c>
-      <c r="I20" s="3">
-        <v>100</v>
       </c>
       <c r="J20" s="3">
         <v>100</v>
       </c>
       <c r="K20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1787,11 +1821,11 @@
         <v>0</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>200</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
@@ -1807,8 +1841,11 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1816,29 +1853,29 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-3200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-800</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1899,8 +1936,11 @@
       <c r="AF21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1910,8 +1950,8 @@
       <c r="E22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
@@ -1949,8 +1989,8 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>4</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>4</v>
@@ -1970,8 +2010,8 @@
       <c r="Y22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
+      <c r="Z22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
@@ -1991,37 +2031,40 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2800</v>
+        <v>-600</v>
       </c>
       <c r="E23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-3200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-800</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-1000</v>
       </c>
       <c r="M23" s="3">
         <v>-1000</v>
@@ -2030,22 +2073,22 @@
         <v>-1000</v>
       </c>
       <c r="O23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P23" s="3">
         <v>-800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-900</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-1100</v>
       </c>
       <c r="U23" s="3">
         <v>-1100</v>
@@ -2054,37 +2097,40 @@
         <v>-1100</v>
       </c>
       <c r="W23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="X23" s="3">
         <v>-700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2175,8 +2221,11 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,37 +2316,40 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2800</v>
+        <v>-600</v>
       </c>
       <c r="E26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-3200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-800</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-1000</v>
       </c>
       <c r="M26" s="3">
         <v>-1000</v>
@@ -2306,22 +2358,22 @@
         <v>-1000</v>
       </c>
       <c r="O26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P26" s="3">
         <v>-800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-900</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-1100</v>
       </c>
       <c r="U26" s="3">
         <v>-1100</v>
@@ -2330,66 +2382,69 @@
         <v>-1100</v>
       </c>
       <c r="W26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="X26" s="3">
         <v>-700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-2300</v>
+        <v>-5600</v>
       </c>
       <c r="E27" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-6800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-800</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-1000</v>
       </c>
       <c r="M27" s="3">
         <v>-1000</v>
@@ -2398,22 +2453,22 @@
         <v>-1000</v>
       </c>
       <c r="O27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P27" s="3">
         <v>-800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-900</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-1100</v>
       </c>
       <c r="U27" s="3">
         <v>-1100</v>
@@ -2422,37 +2477,40 @@
         <v>-1100</v>
       </c>
       <c r="W27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="X27" s="3">
         <v>-700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2886,11 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2828,25 +2898,25 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F32" s="3">
         <v>1100</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-800</v>
       </c>
       <c r="G32" s="3">
         <v>-800</v>
       </c>
       <c r="H32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I32" s="3">
         <v>-400</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-100</v>
       </c>
       <c r="J32" s="3">
         <v>-100</v>
       </c>
       <c r="K32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -2891,11 +2961,11 @@
         <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-200</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
@@ -2911,37 +2981,40 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-2300</v>
+        <v>-5600</v>
       </c>
       <c r="E33" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-6800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-800</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-1000</v>
       </c>
       <c r="M33" s="3">
         <v>-1000</v>
@@ -2950,22 +3023,22 @@
         <v>-1000</v>
       </c>
       <c r="O33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P33" s="3">
         <v>-800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-900</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-1100</v>
       </c>
       <c r="U33" s="3">
         <v>-1100</v>
@@ -2974,37 +3047,40 @@
         <v>-1100</v>
       </c>
       <c r="W33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="X33" s="3">
         <v>-700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,37 +3171,40 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-2300</v>
+        <v>-5600</v>
       </c>
       <c r="E35" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-6800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-800</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-1000</v>
       </c>
       <c r="M35" s="3">
         <v>-1000</v>
@@ -3134,22 +3213,22 @@
         <v>-1000</v>
       </c>
       <c r="O35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P35" s="3">
         <v>-800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-900</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-1100</v>
       </c>
       <c r="U35" s="3">
         <v>-1100</v>
@@ -3158,134 +3237,140 @@
         <v>-1100</v>
       </c>
       <c r="W35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="X35" s="3">
         <v>-700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
         <v>45230</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45138</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45046</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44957</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44865</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44773</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44592</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44500</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44316</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44227</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44135</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44043</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43951</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43861</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43769</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43677</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43585</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43496</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43404</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43312</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43220</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43131</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43039</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42947</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42855</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42766</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3438,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>61200</v>
+      </c>
+      <c r="E41" s="3">
         <v>73400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>74700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>68000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>72600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>77000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>82200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>85400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>86600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>86900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>100</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
-      </c>
       <c r="U41" s="3">
+        <v>0</v>
+      </c>
+      <c r="V41" s="3">
         <v>300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,8 +3626,11 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3628,8 +3721,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,8 +3816,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3729,40 +3828,40 @@
         <v>300</v>
       </c>
       <c r="E45" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F45" s="3">
         <v>100</v>
       </c>
       <c r="G45" s="3">
+        <v>100</v>
+      </c>
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
       <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
         <v>100</v>
-      </c>
-      <c r="K45" s="3">
-        <v>200</v>
       </c>
       <c r="L45" s="3">
         <v>200</v>
       </c>
       <c r="M45" s="3">
+        <v>200</v>
+      </c>
+      <c r="N45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="3">
         <v>100</v>
@@ -3774,28 +3873,28 @@
         <v>100</v>
       </c>
       <c r="T45" s="3">
+        <v>100</v>
+      </c>
+      <c r="U45" s="3">
         <v>200</v>
-      </c>
-      <c r="U45" s="3">
-        <v>100</v>
       </c>
       <c r="V45" s="3">
         <v>100</v>
       </c>
       <c r="W45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X45" s="3">
         <v>0</v>
       </c>
       <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="3">
         <v>100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>200</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>100</v>
       </c>
       <c r="AB45" s="3">
         <v>100</v>
@@ -3807,110 +3906,116 @@
         <v>100</v>
       </c>
       <c r="AE45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>61500</v>
+      </c>
+      <c r="E46" s="3">
         <v>73700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>74800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>68100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>72800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>77200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>82300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>85500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>86800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>87200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1000</v>
-      </c>
-      <c r="S46" s="3">
-        <v>200</v>
       </c>
       <c r="T46" s="3">
         <v>200</v>
       </c>
       <c r="U46" s="3">
+        <v>200</v>
+      </c>
+      <c r="V46" s="3">
         <v>500</v>
-      </c>
-      <c r="V46" s="3">
-        <v>700</v>
       </c>
       <c r="W46" s="3">
         <v>700</v>
       </c>
       <c r="X46" s="3">
+        <v>700</v>
+      </c>
+      <c r="Y46" s="3">
         <v>900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1600</v>
+        <v>3600</v>
       </c>
       <c r="E47" s="3">
         <v>1600</v>
@@ -3996,8 +4101,11 @@
       <c r="AF47" s="3">
         <v>1600</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4088,8 +4196,11 @@
       <c r="AF48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4291,11 @@
       <c r="AF49" s="3">
         <v>3500</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,13 +4481,16 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
@@ -4456,8 +4576,11 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4671,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>71400</v>
+      </c>
+      <c r="E54" s="3">
         <v>78900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>79900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>73300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>78000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>82300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>87400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>90600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>91900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>92300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6200</v>
-      </c>
-      <c r="S54" s="3">
-        <v>5300</v>
       </c>
       <c r="T54" s="3">
         <v>5300</v>
       </c>
       <c r="U54" s="3">
+        <v>5300</v>
+      </c>
+      <c r="V54" s="3">
         <v>5600</v>
-      </c>
-      <c r="V54" s="3">
-        <v>5800</v>
       </c>
       <c r="W54" s="3">
         <v>5800</v>
       </c>
       <c r="X54" s="3">
+        <v>5800</v>
+      </c>
+      <c r="Y54" s="3">
         <v>6100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>9500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>8700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,64 +4838,65 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>500</v>
+      </c>
+      <c r="E57" s="3">
         <v>100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>200</v>
-      </c>
-      <c r="O57" s="3">
-        <v>100</v>
       </c>
       <c r="P57" s="3">
         <v>100</v>
       </c>
       <c r="Q57" s="3">
+        <v>100</v>
+      </c>
+      <c r="R57" s="3">
         <v>400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>200</v>
-      </c>
-      <c r="U57" s="3">
-        <v>100</v>
       </c>
       <c r="V57" s="3">
         <v>100</v>
@@ -4774,34 +4905,37 @@
         <v>100</v>
       </c>
       <c r="X57" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y57" s="3">
         <v>300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>400</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>300</v>
       </c>
       <c r="AB57" s="3">
         <v>300</v>
       </c>
       <c r="AC57" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD57" s="3">
         <v>600</v>
-      </c>
-      <c r="AD57" s="3">
-        <v>400</v>
       </c>
       <c r="AE57" s="3">
         <v>400</v>
       </c>
       <c r="AF57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4839,19 +4973,19 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P58" s="3">
         <v>100</v>
       </c>
       <c r="Q58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>4</v>
+      <c r="S58" s="3">
+        <v>0</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>4</v>
@@ -4868,8 +5002,8 @@
       <c r="X58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -4892,28 +5026,31 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E59" s="3">
         <v>5100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>500</v>
-      </c>
-      <c r="G59" s="3">
-        <v>400</v>
       </c>
       <c r="H59" s="3">
         <v>400</v>
       </c>
       <c r="I59" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J59" s="3">
         <v>500</v>
@@ -4922,40 +5059,40 @@
         <v>500</v>
       </c>
       <c r="L59" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="M59" s="3">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3">
         <v>500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>600</v>
-      </c>
-      <c r="O59" s="3">
-        <v>500</v>
       </c>
       <c r="P59" s="3">
         <v>500</v>
       </c>
       <c r="Q59" s="3">
+        <v>500</v>
+      </c>
+      <c r="R59" s="3">
         <v>700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>600</v>
-      </c>
-      <c r="W59" s="3">
-        <v>300</v>
       </c>
       <c r="X59" s="3">
         <v>300</v>
@@ -4967,117 +5104,123 @@
         <v>300</v>
       </c>
       <c r="AA59" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB59" s="3">
         <v>600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>300</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>200</v>
       </c>
       <c r="AD59" s="3">
         <v>200</v>
       </c>
       <c r="AE59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AF59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E60" s="3">
         <v>5200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>700</v>
-      </c>
-      <c r="O60" s="3">
-        <v>600</v>
       </c>
       <c r="P60" s="3">
         <v>600</v>
       </c>
       <c r="Q60" s="3">
+        <v>600</v>
+      </c>
+      <c r="R60" s="3">
         <v>1200</v>
-      </c>
-      <c r="R60" s="3">
-        <v>1000</v>
       </c>
       <c r="S60" s="3">
         <v>1000</v>
       </c>
       <c r="T60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U60" s="3">
         <v>800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>900</v>
-      </c>
-      <c r="AD60" s="3">
-        <v>600</v>
       </c>
       <c r="AE60" s="3">
         <v>600</v>
       </c>
       <c r="AF60" s="3">
+        <v>600</v>
+      </c>
+      <c r="AG60" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5168,20 +5311,23 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E62" s="3">
         <v>15600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>18900</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G62" s="3" t="s">
         <v>4</v>
       </c>
@@ -5197,8 +5343,8 @@
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -5260,8 +5406,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5691,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E66" s="3">
         <v>20800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>20400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>900</v>
-      </c>
-      <c r="AD66" s="3">
-        <v>600</v>
       </c>
       <c r="AE66" s="3">
         <v>600</v>
       </c>
       <c r="AF66" s="3">
+        <v>600</v>
+      </c>
+      <c r="AG66" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,20 +6011,23 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E70" s="3">
         <v>21300</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>16800</v>
       </c>
-      <c r="F70" s="3">
-        <v>0</v>
-      </c>
       <c r="G70" s="3">
         <v>0</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6201,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-117000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-116400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-119500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-116000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-115800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-115100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-113200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-111600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-110200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-109400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-108400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-107400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-106400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-105700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-104700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-103900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-103100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-102200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-101200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-100000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-98900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-98200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-97200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-96000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-94700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-92600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-90800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-89100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-88000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-86700</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6581,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>31400</v>
+      </c>
+      <c r="E76" s="3">
         <v>36800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>42700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>72700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>77100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>81000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>86300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>89900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>91300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>92100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4500</v>
-      </c>
-      <c r="U76" s="3">
-        <v>5000</v>
       </c>
       <c r="V76" s="3">
         <v>5000</v>
       </c>
       <c r="W76" s="3">
-        <v>5400</v>
+        <v>5000</v>
       </c>
       <c r="X76" s="3">
         <v>5400</v>
       </c>
       <c r="Y76" s="3">
+        <v>5400</v>
+      </c>
+      <c r="Z76" s="3">
         <v>6200</v>
-      </c>
-      <c r="Z76" s="3">
-        <v>5800</v>
       </c>
       <c r="AA76" s="3">
         <v>5800</v>
       </c>
       <c r="AB76" s="3">
+        <v>5800</v>
+      </c>
+      <c r="AC76" s="3">
         <v>7300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>8100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,134 +6771,140 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
         <v>45230</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45138</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45046</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44957</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44865</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44773</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44592</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44500</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44316</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44227</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44135</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44043</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43951</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43861</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43769</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43677</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43585</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43496</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43404</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43312</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43220</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43131</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43039</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42947</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42855</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42766</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-2300</v>
+        <v>-5600</v>
       </c>
       <c r="E81" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-6800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-800</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-1000</v>
       </c>
       <c r="M81" s="3">
         <v>-1000</v>
@@ -6718,22 +6913,22 @@
         <v>-1000</v>
       </c>
       <c r="O81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P81" s="3">
         <v>-800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-900</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-1100</v>
       </c>
       <c r="U81" s="3">
         <v>-1100</v>
@@ -6742,37 +6937,40 @@
         <v>-1100</v>
       </c>
       <c r="W81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="X81" s="3">
         <v>-700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7003,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6897,8 +7096,11 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7571,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-2000</v>
+        <v>-200</v>
       </c>
       <c r="E89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F89" s="3">
         <v>300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1300</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-600</v>
       </c>
       <c r="R89" s="3">
         <v>-600</v>
       </c>
       <c r="S89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="T89" s="3">
         <v>-400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-800</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-700</v>
       </c>
       <c r="W89" s="3">
         <v>-700</v>
       </c>
       <c r="X89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7703,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7575,8 +7796,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,13 +7986,16 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -7779,11 +8009,11 @@
       <c r="H94" s="3">
         <v>0</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -7851,8 +8081,11 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,88 +8496,91 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>700</v>
+        <v>-7000</v>
       </c>
       <c r="E100" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F100" s="3">
         <v>6300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>87400</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>2800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>600</v>
-      </c>
-      <c r="V100" s="3">
-        <v>500</v>
       </c>
       <c r="W100" s="3">
         <v>500</v>
       </c>
       <c r="X100" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>1400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>900</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
         <v>0</v>
       </c>
       <c r="AC100" s="3">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="AD100" s="3">
         <v>1800</v>
@@ -8343,10 +8589,13 @@
         <v>1800</v>
       </c>
       <c r="AF100" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,64 +8686,67 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F102" s="3">
+        <v>6600</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="K102" s="3">
         <v>-1200</v>
       </c>
-      <c r="E102" s="3">
-        <v>6600</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M102" s="3">
+        <v>86000</v>
+      </c>
+      <c r="N102" s="3">
         <v>-1200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="O102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>1600</v>
+      </c>
+      <c r="R102" s="3">
+        <v>1300</v>
+      </c>
+      <c r="S102" s="3">
+        <v>800</v>
+      </c>
+      <c r="T102" s="3">
+        <v>100</v>
+      </c>
+      <c r="U102" s="3">
         <v>-300</v>
-      </c>
-      <c r="L102" s="3">
-        <v>86000</v>
-      </c>
-      <c r="M102" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="N102" s="3">
-        <v>-900</v>
-      </c>
-      <c r="O102" s="3">
-        <v>-600</v>
-      </c>
-      <c r="P102" s="3">
-        <v>1600</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>1300</v>
-      </c>
-      <c r="R102" s="3">
-        <v>800</v>
-      </c>
-      <c r="S102" s="3">
-        <v>100</v>
-      </c>
-      <c r="T102" s="3">
-        <v>-300</v>
-      </c>
-      <c r="U102" s="3">
-        <v>-200</v>
       </c>
       <c r="V102" s="3">
         <v>-200</v>
@@ -8503,30 +8755,33 @@
         <v>-200</v>
       </c>
       <c r="X102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PMCB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PMCB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
   <si>
     <t>PMCB</t>
   </si>
@@ -656,144 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E7" s="2">
         <v>45322</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45138</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45046</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44957</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44865</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44773</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44592</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44500</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44316</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44227</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44043</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43951</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43861</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43769</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43677</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43585</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43496</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43404</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43312</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43220</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43131</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43039</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42947</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42855</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42766</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -887,8 +890,11 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -982,8 +988,11 @@
       <c r="AG9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1077,8 +1086,11 @@
       <c r="AG10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1112,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1121,94 +1134,97 @@
         <v>100</v>
       </c>
       <c r="E12" s="3">
+        <v>100</v>
+      </c>
+      <c r="F12" s="3">
         <v>200</v>
-      </c>
-      <c r="F12" s="3">
-        <v>100</v>
       </c>
       <c r="G12" s="3">
         <v>100</v>
       </c>
       <c r="H12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I12" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3">
         <v>200</v>
       </c>
       <c r="K12" s="3">
+        <v>200</v>
+      </c>
+      <c r="L12" s="3">
         <v>300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>200</v>
-      </c>
-      <c r="M12" s="3">
-        <v>100</v>
       </c>
       <c r="N12" s="3">
         <v>100</v>
       </c>
       <c r="O12" s="3">
+        <v>100</v>
+      </c>
+      <c r="P12" s="3">
         <v>300</v>
-      </c>
-      <c r="P12" s="3">
-        <v>200</v>
       </c>
       <c r="Q12" s="3">
         <v>200</v>
       </c>
       <c r="R12" s="3">
+        <v>200</v>
+      </c>
+      <c r="S12" s="3">
         <v>300</v>
-      </c>
-      <c r="S12" s="3">
-        <v>100</v>
       </c>
       <c r="T12" s="3">
         <v>100</v>
       </c>
       <c r="U12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V12" s="3">
+        <v>0</v>
+      </c>
+      <c r="W12" s="3">
         <v>100</v>
       </c>
-      <c r="W12" s="3">
-        <v>0</v>
-      </c>
       <c r="X12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="3">
         <v>100</v>
       </c>
       <c r="Z12" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AA12" s="3">
         <v>300</v>
       </c>
       <c r="AB12" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC12" s="3">
         <v>800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,13 +1318,16 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>2000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>4</v>
@@ -1328,11 +1347,11 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
@@ -1340,12 +1359,12 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3">
         <v>-100</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1361,8 +1380,8 @@
       <c r="U14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1397,8 +1416,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1492,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,40 +1549,41 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E17" s="3">
         <v>1900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>900</v>
-      </c>
-      <c r="M17" s="3">
-        <v>1000</v>
       </c>
       <c r="N17" s="3">
         <v>1000</v>
@@ -1566,61 +1592,64 @@
         <v>1000</v>
       </c>
       <c r="P17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q17" s="3">
         <v>800</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>900</v>
       </c>
       <c r="R17" s="3">
         <v>900</v>
       </c>
       <c r="S17" s="3">
+        <v>900</v>
+      </c>
+      <c r="T17" s="3">
         <v>700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>900</v>
-      </c>
-      <c r="U17" s="3">
-        <v>1100</v>
       </c>
       <c r="V17" s="3">
         <v>1100</v>
       </c>
       <c r="W17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X17" s="3">
         <v>1200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1628,31 +1657,31 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-900</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-1000</v>
       </c>
       <c r="N18" s="3">
         <v>-1000</v>
@@ -1661,61 +1690,64 @@
         <v>-1000</v>
       </c>
       <c r="P18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-800</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-900</v>
       </c>
       <c r="R18" s="3">
         <v>-900</v>
       </c>
       <c r="S18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="T18" s="3">
         <v>-700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-900</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-1100</v>
       </c>
       <c r="V18" s="3">
         <v>-1100</v>
       </c>
       <c r="W18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="X18" s="3">
         <v>-1200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,8 +1781,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1758,28 +1791,28 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F20" s="3">
         <v>3100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>800</v>
       </c>
       <c r="H20" s="3">
         <v>800</v>
       </c>
       <c r="I20" s="3">
+        <v>800</v>
+      </c>
+      <c r="J20" s="3">
         <v>400</v>
-      </c>
-      <c r="J20" s="3">
-        <v>100</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
       </c>
       <c r="L20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1824,11 +1857,11 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>200</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
@@ -1844,8 +1877,11 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1853,32 +1889,32 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-800</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1939,8 +1975,11 @@
       <c r="AG21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1953,8 +1992,8 @@
       <c r="F22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -1992,8 +2031,8 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>4</v>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>4</v>
@@ -2013,8 +2052,8 @@
       <c r="Z22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -2034,40 +2073,43 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-800</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-1000</v>
       </c>
       <c r="N23" s="3">
         <v>-1000</v>
@@ -2076,22 +2118,22 @@
         <v>-1000</v>
       </c>
       <c r="P23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-900</v>
-      </c>
-      <c r="U23" s="3">
-        <v>-1100</v>
       </c>
       <c r="V23" s="3">
         <v>-1100</v>
@@ -2100,37 +2142,40 @@
         <v>-1100</v>
       </c>
       <c r="X23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2224,8 +2269,11 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,40 +2367,43 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-800</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-1000</v>
       </c>
       <c r="N26" s="3">
         <v>-1000</v>
@@ -2361,22 +2412,22 @@
         <v>-1000</v>
       </c>
       <c r="P26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-900</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-1100</v>
       </c>
       <c r="V26" s="3">
         <v>-1100</v>
@@ -2385,69 +2436,72 @@
         <v>-1100</v>
       </c>
       <c r="X26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-800</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-1000</v>
       </c>
       <c r="N27" s="3">
         <v>-1000</v>
@@ -2456,22 +2510,22 @@
         <v>-1000</v>
       </c>
       <c r="P27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-900</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-1100</v>
       </c>
       <c r="V27" s="3">
         <v>-1100</v>
@@ -2480,37 +2534,40 @@
         <v>-1100</v>
       </c>
       <c r="X27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2699,8 +2759,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,8 +2955,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2898,28 +2967,28 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-3100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-800</v>
       </c>
       <c r="H32" s="3">
         <v>-800</v>
       </c>
       <c r="I32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J32" s="3">
         <v>-400</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-100</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
       </c>
       <c r="L32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -2964,11 +3033,11 @@
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-200</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
@@ -2984,40 +3053,43 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-800</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-1000</v>
       </c>
       <c r="N33" s="3">
         <v>-1000</v>
@@ -3026,22 +3098,22 @@
         <v>-1000</v>
       </c>
       <c r="P33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-900</v>
-      </c>
-      <c r="U33" s="3">
-        <v>-1100</v>
       </c>
       <c r="V33" s="3">
         <v>-1100</v>
@@ -3050,37 +3122,40 @@
         <v>-1100</v>
       </c>
       <c r="X33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,40 +3249,43 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-800</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-1000</v>
       </c>
       <c r="N35" s="3">
         <v>-1000</v>
@@ -3216,22 +3294,22 @@
         <v>-1000</v>
       </c>
       <c r="P35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-900</v>
-      </c>
-      <c r="U35" s="3">
-        <v>-1100</v>
       </c>
       <c r="V35" s="3">
         <v>-1100</v>
@@ -3240,137 +3318,143 @@
         <v>-1100</v>
       </c>
       <c r="X35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E38" s="2">
         <v>45322</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45138</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45046</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44957</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44865</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44773</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44592</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44500</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44316</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44227</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44043</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43951</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43861</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43769</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43677</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43585</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43496</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43404</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43312</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43220</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43131</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43039</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42947</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42855</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42766</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,103 +3524,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>50200</v>
+      </c>
+      <c r="E41" s="3">
         <v>61200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>73400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>74700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>68000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>72600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>77000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>82200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>85400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>86600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>86900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>100</v>
       </c>
-      <c r="U41" s="3">
-        <v>0</v>
-      </c>
       <c r="V41" s="3">
+        <v>0</v>
+      </c>
+      <c r="W41" s="3">
         <v>300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3629,8 +3718,11 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3724,8 +3816,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3819,8 +3914,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3831,40 +3929,40 @@
         <v>300</v>
       </c>
       <c r="F45" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G45" s="3">
         <v>100</v>
       </c>
       <c r="H45" s="3">
+        <v>100</v>
+      </c>
+      <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
       <c r="K45" s="3">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3">
         <v>100</v>
-      </c>
-      <c r="L45" s="3">
-        <v>200</v>
       </c>
       <c r="M45" s="3">
         <v>200</v>
       </c>
       <c r="N45" s="3">
+        <v>200</v>
+      </c>
+      <c r="O45" s="3">
         <v>500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R45" s="3">
         <v>100</v>
@@ -3876,28 +3974,28 @@
         <v>100</v>
       </c>
       <c r="U45" s="3">
+        <v>100</v>
+      </c>
+      <c r="V45" s="3">
         <v>200</v>
-      </c>
-      <c r="V45" s="3">
-        <v>100</v>
       </c>
       <c r="W45" s="3">
         <v>100</v>
       </c>
       <c r="X45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y45" s="3">
         <v>0</v>
       </c>
       <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="3">
         <v>100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>200</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>100</v>
       </c>
       <c r="AC45" s="3">
         <v>100</v>
@@ -3909,116 +4007,122 @@
         <v>100</v>
       </c>
       <c r="AF45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E46" s="3">
         <v>61500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>73700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>74800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>68100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>72800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>77200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>82300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>85500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>86800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>87200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1000</v>
-      </c>
-      <c r="T46" s="3">
-        <v>200</v>
       </c>
       <c r="U46" s="3">
         <v>200</v>
       </c>
       <c r="V46" s="3">
+        <v>200</v>
+      </c>
+      <c r="W46" s="3">
         <v>500</v>
-      </c>
-      <c r="W46" s="3">
-        <v>700</v>
       </c>
       <c r="X46" s="3">
         <v>700</v>
       </c>
       <c r="Y46" s="3">
+        <v>700</v>
+      </c>
+      <c r="Z46" s="3">
         <v>900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E47" s="3">
         <v>3600</v>
-      </c>
-      <c r="E47" s="3">
-        <v>1600</v>
       </c>
       <c r="F47" s="3">
         <v>1600</v>
@@ -4104,8 +4208,11 @@
       <c r="AG47" s="3">
         <v>1600</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4199,13 +4306,16 @@
       <c r="AG48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="E49" s="3">
         <v>3500</v>
@@ -4294,8 +4404,11 @@
       <c r="AG49" s="3">
         <v>3500</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,17 +4600,20 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E52" s="3">
         <v>2700</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
       <c r="F52" s="3">
         <v>0</v>
       </c>
@@ -4579,8 +4698,11 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>59900</v>
+      </c>
+      <c r="E54" s="3">
         <v>71400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>78900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>79900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>73300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>78000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>82300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>87400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>90600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>91900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>92300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6200</v>
-      </c>
-      <c r="T54" s="3">
-        <v>5300</v>
       </c>
       <c r="U54" s="3">
         <v>5300</v>
       </c>
       <c r="V54" s="3">
+        <v>5300</v>
+      </c>
+      <c r="W54" s="3">
         <v>5600</v>
-      </c>
-      <c r="W54" s="3">
-        <v>5800</v>
       </c>
       <c r="X54" s="3">
         <v>5800</v>
       </c>
       <c r="Y54" s="3">
+        <v>5800</v>
+      </c>
+      <c r="Z54" s="3">
         <v>6100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>9500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>8700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>7600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,67 +4968,68 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400</v>
+      </c>
+      <c r="E57" s="3">
         <v>500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>200</v>
-      </c>
-      <c r="P57" s="3">
-        <v>100</v>
       </c>
       <c r="Q57" s="3">
         <v>100</v>
       </c>
       <c r="R57" s="3">
+        <v>100</v>
+      </c>
+      <c r="S57" s="3">
         <v>400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>200</v>
-      </c>
-      <c r="V57" s="3">
-        <v>100</v>
       </c>
       <c r="W57" s="3">
         <v>100</v>
@@ -4908,34 +5038,37 @@
         <v>100</v>
       </c>
       <c r="Y57" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z57" s="3">
         <v>300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>400</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>300</v>
       </c>
       <c r="AC57" s="3">
         <v>300</v>
       </c>
       <c r="AD57" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE57" s="3">
         <v>600</v>
-      </c>
-      <c r="AE57" s="3">
-        <v>400</v>
       </c>
       <c r="AF57" s="3">
         <v>400</v>
       </c>
       <c r="AG57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4976,19 +5109,19 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="3">
         <v>100</v>
       </c>
       <c r="R58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>4</v>
+      <c r="T58" s="3">
+        <v>0</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>4</v>
@@ -5005,8 +5138,8 @@
       <c r="Y58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="Z58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
@@ -5029,31 +5162,34 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E59" s="3">
         <v>7100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>500</v>
-      </c>
-      <c r="H59" s="3">
-        <v>400</v>
       </c>
       <c r="I59" s="3">
         <v>400</v>
       </c>
       <c r="J59" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K59" s="3">
         <v>500</v>
@@ -5062,40 +5198,40 @@
         <v>500</v>
       </c>
       <c r="M59" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="N59" s="3">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3">
         <v>500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>600</v>
-      </c>
-      <c r="P59" s="3">
-        <v>500</v>
       </c>
       <c r="Q59" s="3">
         <v>500</v>
       </c>
       <c r="R59" s="3">
+        <v>500</v>
+      </c>
+      <c r="S59" s="3">
         <v>700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>600</v>
-      </c>
-      <c r="X59" s="3">
-        <v>300</v>
       </c>
       <c r="Y59" s="3">
         <v>300</v>
@@ -5107,120 +5243,126 @@
         <v>300</v>
       </c>
       <c r="AB59" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC59" s="3">
         <v>600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>300</v>
-      </c>
-      <c r="AD59" s="3">
-        <v>200</v>
       </c>
       <c r="AE59" s="3">
         <v>200</v>
       </c>
       <c r="AF59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AG59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E60" s="3">
         <v>7500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>700</v>
-      </c>
-      <c r="P60" s="3">
-        <v>600</v>
       </c>
       <c r="Q60" s="3">
         <v>600</v>
       </c>
       <c r="R60" s="3">
+        <v>600</v>
+      </c>
+      <c r="S60" s="3">
         <v>1200</v>
-      </c>
-      <c r="S60" s="3">
-        <v>1000</v>
       </c>
       <c r="T60" s="3">
         <v>1000</v>
       </c>
       <c r="U60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V60" s="3">
         <v>800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>900</v>
-      </c>
-      <c r="AE60" s="3">
-        <v>600</v>
       </c>
       <c r="AF60" s="3">
         <v>600</v>
       </c>
       <c r="AG60" s="3">
+        <v>600</v>
+      </c>
+      <c r="AH60" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5314,23 +5456,26 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E62" s="3">
         <v>14900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>15600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>18900</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H62" s="3" t="s">
         <v>4</v>
       </c>
@@ -5346,8 +5491,8 @@
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -5409,8 +5554,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E66" s="3">
         <v>22500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>20800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>20400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>900</v>
-      </c>
-      <c r="AE66" s="3">
-        <v>600</v>
       </c>
       <c r="AF66" s="3">
         <v>600</v>
       </c>
       <c r="AG66" s="3">
+        <v>600</v>
+      </c>
+      <c r="AH66" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,23 +6178,26 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E70" s="3">
         <v>17500</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>21300</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>16800</v>
       </c>
-      <c r="G70" s="3">
-        <v>0</v>
-      </c>
       <c r="H70" s="3">
         <v>0</v>
       </c>
@@ -6109,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-115600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-117000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-116400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-119500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-116000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-115800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-115100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-113200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-111600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-110200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-109400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-108400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-107400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-106400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-105700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-104700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-103900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-103100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-102200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-101200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-100000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-98900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-98200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-97200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-96000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-94700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-92600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-90800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-89100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-88000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-86700</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E76" s="3">
         <v>31400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>36800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>42700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>72700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>77100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>81000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>86300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>89900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>91300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>92100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4500</v>
-      </c>
-      <c r="V76" s="3">
-        <v>5000</v>
       </c>
       <c r="W76" s="3">
         <v>5000</v>
       </c>
       <c r="X76" s="3">
-        <v>5400</v>
+        <v>5000</v>
       </c>
       <c r="Y76" s="3">
         <v>5400</v>
       </c>
       <c r="Z76" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AA76" s="3">
         <v>6200</v>
-      </c>
-      <c r="AA76" s="3">
-        <v>5800</v>
       </c>
       <c r="AB76" s="3">
         <v>5800</v>
       </c>
       <c r="AC76" s="3">
+        <v>5800</v>
+      </c>
+      <c r="AD76" s="3">
         <v>7300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>8700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>8100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,140 +6962,146 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E80" s="2">
         <v>45322</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45138</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45046</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44957</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44865</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44773</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44592</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44500</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44316</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44227</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44043</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43951</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43861</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43769</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43677</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43585</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43496</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43404</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43312</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43220</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43131</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43039</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42947</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42855</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42766</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-800</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-1000</v>
       </c>
       <c r="N81" s="3">
         <v>-1000</v>
@@ -6916,22 +7110,22 @@
         <v>-1000</v>
       </c>
       <c r="P81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-900</v>
-      </c>
-      <c r="U81" s="3">
-        <v>-1100</v>
       </c>
       <c r="V81" s="3">
         <v>-1100</v>
@@ -6940,37 +7134,40 @@
         <v>-1100</v>
       </c>
       <c r="X81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7099,8 +7297,11 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1300</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-600</v>
       </c>
       <c r="S89" s="3">
         <v>-600</v>
       </c>
       <c r="T89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="U89" s="3">
         <v>-400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-800</v>
-      </c>
-      <c r="W89" s="3">
-        <v>-700</v>
       </c>
       <c r="X89" s="3">
         <v>-700</v>
       </c>
       <c r="Y89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,8 +7923,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7799,8 +8019,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,17 +8215,20 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5000</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
@@ -8009,14 +8238,14 @@
       <c r="H94" s="3">
         <v>0</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
+      <c r="I94" s="3">
+        <v>0</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -8084,8 +8313,11 @@
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8214,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,91 +8741,94 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-7000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>7000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>87400</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>2800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>600</v>
-      </c>
-      <c r="W100" s="3">
-        <v>500</v>
       </c>
       <c r="X100" s="3">
         <v>500</v>
       </c>
       <c r="Y100" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>1400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>900</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
         <v>0</v>
       </c>
       <c r="AD100" s="3">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="AE100" s="3">
         <v>1800</v>
@@ -8592,10 +8837,13 @@
         <v>1800</v>
       </c>
       <c r="AG100" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8689,67 +8937,70 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-12200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>86000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-300</v>
-      </c>
-      <c r="V102" s="3">
-        <v>-200</v>
       </c>
       <c r="W102" s="3">
         <v>-200</v>
@@ -8758,30 +9009,33 @@
         <v>-200</v>
       </c>
       <c r="Y102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PMCB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PMCB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
   <si>
     <t>PMCB</t>
   </si>
@@ -656,170 +656,174 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E7" s="2">
         <v>45412</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45322</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45230</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45138</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44957</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44865</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44773</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44592</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44500</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44316</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44227</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44135</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44043</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43951</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43861</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43769</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43677</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43585</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43496</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43404</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43312</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43220</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43131</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43039</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42947</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42855</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42766</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -893,8 +897,11 @@
       <c r="AH8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -991,8 +998,11 @@
       <c r="AH9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1089,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1137,7 +1151,7 @@
         <v>100</v>
       </c>
       <c r="F12" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G12" s="3">
         <v>100</v>
@@ -1146,85 +1160,88 @@
         <v>100</v>
       </c>
       <c r="I12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K12" s="3">
         <v>200</v>
       </c>
       <c r="L12" s="3">
+        <v>200</v>
+      </c>
+      <c r="M12" s="3">
         <v>300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>200</v>
-      </c>
-      <c r="N12" s="3">
-        <v>100</v>
       </c>
       <c r="O12" s="3">
         <v>100</v>
       </c>
       <c r="P12" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q12" s="3">
         <v>300</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>200</v>
       </c>
       <c r="R12" s="3">
         <v>200</v>
       </c>
       <c r="S12" s="3">
+        <v>200</v>
+      </c>
+      <c r="T12" s="3">
         <v>300</v>
-      </c>
-      <c r="T12" s="3">
-        <v>100</v>
       </c>
       <c r="U12" s="3">
         <v>100</v>
       </c>
       <c r="V12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W12" s="3">
+        <v>0</v>
+      </c>
+      <c r="X12" s="3">
         <v>100</v>
       </c>
-      <c r="X12" s="3">
-        <v>0</v>
-      </c>
       <c r="Y12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="3">
         <v>100</v>
       </c>
       <c r="AA12" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AB12" s="3">
         <v>300</v>
       </c>
       <c r="AC12" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD12" s="3">
         <v>800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,17 +1338,20 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="E14" s="3">
         <v>2000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1350,11 +1370,11 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
@@ -1362,12 +1382,12 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-100</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1383,8 +1403,8 @@
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,43 +1576,44 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3200</v>
+        <v>1300</v>
       </c>
       <c r="E17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F17" s="3">
         <v>1900</v>
       </c>
-      <c r="F17" s="3">
-        <v>3500</v>
-      </c>
       <c r="G17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H17" s="3">
         <v>2100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>900</v>
-      </c>
-      <c r="N17" s="3">
-        <v>1000</v>
       </c>
       <c r="O17" s="3">
         <v>1000</v>
@@ -1595,96 +1622,99 @@
         <v>1000</v>
       </c>
       <c r="Q17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R17" s="3">
         <v>800</v>
-      </c>
-      <c r="R17" s="3">
-        <v>900</v>
       </c>
       <c r="S17" s="3">
         <v>900</v>
       </c>
       <c r="T17" s="3">
+        <v>900</v>
+      </c>
+      <c r="U17" s="3">
         <v>700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>900</v>
-      </c>
-      <c r="V17" s="3">
-        <v>1100</v>
       </c>
       <c r="W17" s="3">
         <v>1100</v>
       </c>
       <c r="X17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Y17" s="3">
         <v>1200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-1300</v>
       </c>
       <c r="E18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1900</v>
       </c>
-      <c r="F18" s="3">
-        <v>-3500</v>
-      </c>
       <c r="G18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="H18" s="3">
         <v>-2100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-900</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-1000</v>
       </c>
       <c r="O18" s="3">
         <v>-1000</v>
@@ -1693,61 +1723,64 @@
         <v>-1000</v>
       </c>
       <c r="Q18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="R18" s="3">
         <v>-800</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-900</v>
       </c>
       <c r="S18" s="3">
         <v>-900</v>
       </c>
       <c r="T18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="U18" s="3">
         <v>-700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-900</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-1100</v>
       </c>
       <c r="W18" s="3">
         <v>-1100</v>
       </c>
       <c r="X18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,40 +1815,41 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>-2000</v>
       </c>
       <c r="E20" s="3">
-        <v>1200</v>
+        <v>-3800</v>
       </c>
       <c r="F20" s="3">
-        <v>3100</v>
+        <v>-400</v>
       </c>
       <c r="G20" s="3">
-        <v>-1100</v>
+        <v>-3300</v>
       </c>
       <c r="H20" s="3">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="I20" s="3">
-        <v>800</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K20" s="3">
         <v>400</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1860,11 +1894,11 @@
         <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>200</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
@@ -1880,44 +1914,47 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>800</v>
       </c>
       <c r="E21" s="3">
-        <v>-600</v>
+        <v>2600</v>
       </c>
       <c r="F21" s="3">
-        <v>-400</v>
+        <v>-1500</v>
       </c>
       <c r="G21" s="3">
-        <v>-3200</v>
+        <v>1900</v>
       </c>
       <c r="H21" s="3">
-        <v>-100</v>
+        <v>-4100</v>
       </c>
       <c r="I21" s="3">
         <v>-800</v>
       </c>
       <c r="J21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K21" s="3">
         <v>-1900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-800</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1978,8 +2015,11 @@
       <c r="AH21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1995,14 +2035,14 @@
       <c r="G22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2034,8 +2074,8 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>4</v>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>4</v>
@@ -2055,8 +2095,8 @@
       <c r="AA22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
@@ -2076,43 +2116,46 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E23" s="3">
         <v>1300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-600</v>
       </c>
-      <c r="F23" s="3">
-        <v>-400</v>
-      </c>
       <c r="G23" s="3">
+        <v>2800</v>
+      </c>
+      <c r="H23" s="3">
         <v>-3200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-800</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-1000</v>
       </c>
       <c r="O23" s="3">
         <v>-1000</v>
@@ -2121,22 +2164,22 @@
         <v>-1000</v>
       </c>
       <c r="Q23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="R23" s="3">
         <v>-800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-900</v>
-      </c>
-      <c r="V23" s="3">
-        <v>-1100</v>
       </c>
       <c r="W23" s="3">
         <v>-1100</v>
@@ -2145,60 +2188,63 @@
         <v>-1100</v>
       </c>
       <c r="Y23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Z23" s="3">
         <v>-700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -2272,8 +2318,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,43 +2419,46 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E26" s="3">
         <v>1300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-600</v>
       </c>
-      <c r="F26" s="3">
-        <v>-400</v>
-      </c>
       <c r="G26" s="3">
+        <v>2800</v>
+      </c>
+      <c r="H26" s="3">
         <v>-3200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-800</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-1000</v>
       </c>
       <c r="O26" s="3">
         <v>-1000</v>
@@ -2415,22 +2467,22 @@
         <v>-1000</v>
       </c>
       <c r="Q26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="R26" s="3">
         <v>-800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-900</v>
-      </c>
-      <c r="V26" s="3">
-        <v>-1100</v>
       </c>
       <c r="W26" s="3">
         <v>-1100</v>
@@ -2439,72 +2491,75 @@
         <v>-1100</v>
       </c>
       <c r="Y26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Z26" s="3">
         <v>-700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5600</v>
       </c>
-      <c r="F27" s="3">
-        <v>-9100</v>
-      </c>
       <c r="G27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="H27" s="3">
         <v>-6800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-800</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-1000</v>
       </c>
       <c r="O27" s="3">
         <v>-1000</v>
@@ -2513,22 +2568,22 @@
         <v>-1000</v>
       </c>
       <c r="Q27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="R27" s="3">
         <v>-800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-900</v>
-      </c>
-      <c r="V27" s="3">
-        <v>-1100</v>
       </c>
       <c r="W27" s="3">
         <v>-1100</v>
@@ -2537,37 +2592,40 @@
         <v>-1100</v>
       </c>
       <c r="Y27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Z27" s="3">
         <v>-700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,40 +3025,43 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>2000</v>
       </c>
       <c r="E32" s="3">
-        <v>-1200</v>
+        <v>3800</v>
       </c>
       <c r="F32" s="3">
-        <v>-3100</v>
+        <v>400</v>
       </c>
       <c r="G32" s="3">
-        <v>1100</v>
+        <v>3300</v>
       </c>
       <c r="H32" s="3">
-        <v>-800</v>
+        <v>-2000</v>
       </c>
       <c r="I32" s="3">
-        <v>-800</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
+        <v>200</v>
+      </c>
+      <c r="K32" s="3">
         <v>-400</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-100</v>
       </c>
       <c r="L32" s="3">
         <v>-100</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -3036,11 +3106,11 @@
         <v>0</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-200</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
@@ -3056,43 +3126,46 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-2500</v>
+        <v>23400</v>
       </c>
       <c r="E33" s="3">
-        <v>-5600</v>
+        <v>1300</v>
       </c>
       <c r="F33" s="3">
-        <v>-9100</v>
+        <v>-600</v>
       </c>
       <c r="G33" s="3">
-        <v>-6800</v>
+        <v>2800</v>
       </c>
       <c r="H33" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="I33" s="3">
         <v>-100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-800</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-1000</v>
       </c>
       <c r="O33" s="3">
         <v>-1000</v>
@@ -3101,22 +3174,22 @@
         <v>-1000</v>
       </c>
       <c r="Q33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="R33" s="3">
         <v>-800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-900</v>
-      </c>
-      <c r="V33" s="3">
-        <v>-1100</v>
       </c>
       <c r="W33" s="3">
         <v>-1100</v>
@@ -3125,37 +3198,40 @@
         <v>-1100</v>
       </c>
       <c r="Y33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Z33" s="3">
         <v>-700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,43 +3328,46 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-2500</v>
+        <v>23400</v>
       </c>
       <c r="E35" s="3">
-        <v>-5600</v>
+        <v>1300</v>
       </c>
       <c r="F35" s="3">
-        <v>-9100</v>
+        <v>-600</v>
       </c>
       <c r="G35" s="3">
-        <v>-6800</v>
+        <v>2800</v>
       </c>
       <c r="H35" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="I35" s="3">
         <v>-100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-800</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-1000</v>
       </c>
       <c r="O35" s="3">
         <v>-1000</v>
@@ -3297,22 +3376,22 @@
         <v>-1000</v>
       </c>
       <c r="Q35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="R35" s="3">
         <v>-800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-900</v>
-      </c>
-      <c r="V35" s="3">
-        <v>-1100</v>
       </c>
       <c r="W35" s="3">
         <v>-1100</v>
@@ -3321,140 +3400,146 @@
         <v>-1100</v>
       </c>
       <c r="Y35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Z35" s="3">
         <v>-700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E38" s="2">
         <v>45412</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45322</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45230</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45138</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44957</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44865</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44773</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44592</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44500</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44316</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44227</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44135</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44043</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43951</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43861</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43769</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43677</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43585</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43496</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43404</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43312</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43220</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43131</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43039</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42947</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42855</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42766</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E41" s="3">
         <v>50200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>61200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>73400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>74700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>68000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>72600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>77000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>82200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>85400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>86600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>86900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>100</v>
       </c>
-      <c r="V41" s="3">
-        <v>0</v>
-      </c>
       <c r="W41" s="3">
+        <v>0</v>
+      </c>
+      <c r="X41" s="3">
         <v>300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,31 +3811,34 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3819,31 +3912,34 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3917,55 +4013,58 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3">
-        <v>300</v>
-      </c>
-      <c r="F45" s="3">
-        <v>300</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3">
         <v>100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>200</v>
-      </c>
-      <c r="J45" s="3">
-        <v>300</v>
-      </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3">
-        <v>100</v>
-      </c>
-      <c r="M45" s="3">
-        <v>200</v>
       </c>
       <c r="N45" s="3">
         <v>200</v>
       </c>
       <c r="O45" s="3">
+        <v>200</v>
+      </c>
+      <c r="P45" s="3">
         <v>500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>100</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S45" s="3">
         <v>100</v>
@@ -3977,28 +4076,28 @@
         <v>100</v>
       </c>
       <c r="V45" s="3">
+        <v>100</v>
+      </c>
+      <c r="W45" s="3">
         <v>200</v>
-      </c>
-      <c r="W45" s="3">
-        <v>100</v>
       </c>
       <c r="X45" s="3">
         <v>100</v>
       </c>
       <c r="Y45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z45" s="3">
         <v>0</v>
       </c>
       <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="3">
         <v>100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>200</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>100</v>
       </c>
       <c r="AD45" s="3">
         <v>100</v>
@@ -4010,119 +4109,125 @@
         <v>100</v>
       </c>
       <c r="AG45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E46" s="3">
         <v>50400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>61500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>73700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>74800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>68100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>72800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>77200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>82300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>85500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>86800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>87200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1000</v>
-      </c>
-      <c r="U46" s="3">
-        <v>200</v>
       </c>
       <c r="V46" s="3">
         <v>200</v>
       </c>
       <c r="W46" s="3">
+        <v>200</v>
+      </c>
+      <c r="X46" s="3">
         <v>500</v>
-      </c>
-      <c r="X46" s="3">
-        <v>700</v>
       </c>
       <c r="Y46" s="3">
         <v>700</v>
       </c>
       <c r="Z46" s="3">
+        <v>700</v>
+      </c>
+      <c r="AA46" s="3">
         <v>900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2800</v>
-      </c>
-      <c r="E47" s="3">
-        <v>3600</v>
+        <v>29100</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F47" s="3">
         <v>1600</v>
@@ -4211,31 +4316,34 @@
       <c r="AH47" s="3">
         <v>1600</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -4309,8 +4417,11 @@
       <c r="AH48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4318,7 +4429,7 @@
         <v>1500</v>
       </c>
       <c r="E49" s="3">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="F49" s="3">
         <v>3500</v>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>3500</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,19 +4720,22 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5200</v>
+        <v>6600</v>
       </c>
       <c r="E52" s="3">
-        <v>2700</v>
+        <v>7900</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>70200</v>
+      </c>
+      <c r="E54" s="3">
         <v>59900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>71400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>78900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>79900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>73300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>78000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>82300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>87400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>90600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>91900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>92300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6200</v>
-      </c>
-      <c r="U54" s="3">
-        <v>5300</v>
       </c>
       <c r="V54" s="3">
         <v>5300</v>
       </c>
       <c r="W54" s="3">
+        <v>5300</v>
+      </c>
+      <c r="X54" s="3">
         <v>5600</v>
-      </c>
-      <c r="X54" s="3">
-        <v>5800</v>
       </c>
       <c r="Y54" s="3">
         <v>5800</v>
       </c>
       <c r="Z54" s="3">
+        <v>5800</v>
+      </c>
+      <c r="AA54" s="3">
         <v>6100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>9500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>8700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,70 +5099,71 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>600</v>
+      </c>
+      <c r="E57" s="3">
         <v>400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>200</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>100</v>
       </c>
       <c r="R57" s="3">
         <v>100</v>
       </c>
       <c r="S57" s="3">
+        <v>100</v>
+      </c>
+      <c r="T57" s="3">
         <v>400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>200</v>
-      </c>
-      <c r="W57" s="3">
-        <v>100</v>
       </c>
       <c r="X57" s="3">
         <v>100</v>
@@ -5041,34 +5172,37 @@
         <v>100</v>
       </c>
       <c r="Z57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA57" s="3">
         <v>300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>400</v>
-      </c>
-      <c r="AC57" s="3">
-        <v>300</v>
       </c>
       <c r="AD57" s="3">
         <v>300</v>
       </c>
       <c r="AE57" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF57" s="3">
         <v>600</v>
-      </c>
-      <c r="AF57" s="3">
-        <v>400</v>
       </c>
       <c r="AG57" s="3">
         <v>400</v>
       </c>
       <c r="AH57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5112,19 +5246,19 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R58" s="3">
         <v>100</v>
       </c>
       <c r="S58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>4</v>
+      <c r="U58" s="3">
+        <v>0</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>4</v>
@@ -5141,8 +5275,8 @@
       <c r="Z58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
@@ -5165,34 +5299,37 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>7000</v>
+        <v>6200</v>
       </c>
       <c r="E59" s="3">
-        <v>7100</v>
+        <v>500</v>
       </c>
       <c r="F59" s="3">
-        <v>5100</v>
+        <v>1000</v>
       </c>
       <c r="G59" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="H59" s="3">
-        <v>500</v>
-      </c>
-      <c r="I59" s="3">
+        <v>300</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
         <v>400</v>
-      </c>
-      <c r="J59" s="3">
-        <v>400</v>
-      </c>
-      <c r="K59" s="3">
-        <v>500</v>
       </c>
       <c r="L59" s="3">
         <v>500</v>
@@ -5201,40 +5338,40 @@
         <v>500</v>
       </c>
       <c r="N59" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="O59" s="3">
+        <v>0</v>
+      </c>
+      <c r="P59" s="3">
         <v>500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>600</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>500</v>
       </c>
       <c r="R59" s="3">
         <v>500</v>
       </c>
       <c r="S59" s="3">
+        <v>500</v>
+      </c>
+      <c r="T59" s="3">
         <v>700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>600</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>300</v>
       </c>
       <c r="Z59" s="3">
         <v>300</v>
@@ -5246,123 +5383,129 @@
         <v>300</v>
       </c>
       <c r="AC59" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD59" s="3">
         <v>600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>300</v>
-      </c>
-      <c r="AE59" s="3">
-        <v>200</v>
       </c>
       <c r="AF59" s="3">
         <v>200</v>
       </c>
       <c r="AG59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AH59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>7400</v>
+        <v>7500</v>
       </c>
       <c r="E60" s="3">
-        <v>7500</v>
+        <v>1600</v>
       </c>
       <c r="F60" s="3">
-        <v>5200</v>
+        <v>2200</v>
       </c>
       <c r="G60" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H60" s="3">
         <v>1500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>700</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>600</v>
       </c>
       <c r="R60" s="3">
         <v>600</v>
       </c>
       <c r="S60" s="3">
+        <v>600</v>
+      </c>
+      <c r="T60" s="3">
         <v>1200</v>
-      </c>
-      <c r="T60" s="3">
-        <v>1000</v>
       </c>
       <c r="U60" s="3">
         <v>1000</v>
       </c>
       <c r="V60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W60" s="3">
         <v>800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>900</v>
-      </c>
-      <c r="AF60" s="3">
-        <v>600</v>
       </c>
       <c r="AG60" s="3">
         <v>600</v>
       </c>
       <c r="AH60" s="3">
+        <v>600</v>
+      </c>
+      <c r="AI60" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5459,26 +5602,29 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E62" s="3">
         <v>13000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>14900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>15600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>18900</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>4</v>
       </c>
@@ -5494,8 +5640,8 @@
       <c r="M62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
+      <c r="N62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>14600</v>
+      </c>
+      <c r="F66" s="3">
+        <v>17200</v>
+      </c>
+      <c r="G66" s="3">
+        <v>17300</v>
+      </c>
+      <c r="H66" s="3">
         <v>20400</v>
       </c>
-      <c r="E66" s="3">
-        <v>22500</v>
-      </c>
-      <c r="F66" s="3">
-        <v>20800</v>
-      </c>
-      <c r="G66" s="3">
-        <v>20400</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>900</v>
-      </c>
-      <c r="AF66" s="3">
-        <v>600</v>
       </c>
       <c r="AG66" s="3">
         <v>600</v>
       </c>
       <c r="AH66" s="3">
+        <v>600</v>
+      </c>
+      <c r="AI66" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,26 +6346,29 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>11900</v>
+        <v>5300</v>
       </c>
       <c r="E70" s="3">
-        <v>17500</v>
+        <v>17700</v>
       </c>
       <c r="F70" s="3">
-        <v>21300</v>
+        <v>22800</v>
       </c>
       <c r="G70" s="3">
+        <v>24800</v>
+      </c>
+      <c r="H70" s="3">
         <v>16800</v>
       </c>
-      <c r="H70" s="3">
-        <v>0</v>
-      </c>
       <c r="I70" s="3">
         <v>0</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-92200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-115600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-117000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-116400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-119500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-116000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-115800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-115100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-113200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-111600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-110200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-109400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-108400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-107400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-106400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-105700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-104700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-103900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-103100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-102200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-101200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-100000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-98900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-98200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-97200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-96000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-94700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-92600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-90800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-89100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-88000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-86700</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>47700</v>
+      </c>
+      <c r="E76" s="3">
         <v>27600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>31400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>36800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>42700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>72700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>77100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>81000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>86300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>89900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>91300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>92100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4500</v>
-      </c>
-      <c r="W76" s="3">
-        <v>5000</v>
       </c>
       <c r="X76" s="3">
         <v>5000</v>
       </c>
       <c r="Y76" s="3">
-        <v>5400</v>
+        <v>5000</v>
       </c>
       <c r="Z76" s="3">
         <v>5400</v>
       </c>
       <c r="AA76" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AB76" s="3">
         <v>6200</v>
-      </c>
-      <c r="AB76" s="3">
-        <v>5800</v>
       </c>
       <c r="AC76" s="3">
         <v>5800</v>
       </c>
       <c r="AD76" s="3">
+        <v>5800</v>
+      </c>
+      <c r="AE76" s="3">
         <v>7300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>8700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>8100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>7000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,146 +7154,152 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E80" s="2">
         <v>45412</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45322</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45230</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45138</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44957</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44865</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44773</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44592</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44500</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44316</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44227</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44135</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44043</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43951</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43861</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43769</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43677</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43585</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43496</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43404</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43312</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43220</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43131</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43039</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42947</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42855</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42766</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-2500</v>
+        <v>23400</v>
       </c>
       <c r="E81" s="3">
-        <v>-5600</v>
+        <v>1300</v>
       </c>
       <c r="F81" s="3">
-        <v>-9100</v>
+        <v>-600</v>
       </c>
       <c r="G81" s="3">
-        <v>-6800</v>
+        <v>2800</v>
       </c>
       <c r="H81" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="I81" s="3">
         <v>-100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-800</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-1000</v>
       </c>
       <c r="O81" s="3">
         <v>-1000</v>
@@ -7113,22 +7308,22 @@
         <v>-1000</v>
       </c>
       <c r="Q81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="R81" s="3">
         <v>-800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-900</v>
-      </c>
-      <c r="V81" s="3">
-        <v>-1100</v>
       </c>
       <c r="W81" s="3">
         <v>-1100</v>
@@ -7137,37 +7332,40 @@
         <v>-1100</v>
       </c>
       <c r="Y81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Z81" s="3">
         <v>-700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,31 +7400,32 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-200</v>
       </c>
-      <c r="F89" s="3">
-        <v>-1600</v>
-      </c>
       <c r="G89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="H89" s="3">
         <v>300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1300</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-600</v>
       </c>
       <c r="T89" s="3">
         <v>-600</v>
       </c>
       <c r="U89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="V89" s="3">
         <v>-400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-800</v>
-      </c>
-      <c r="X89" s="3">
-        <v>-700</v>
       </c>
       <c r="Y89" s="3">
         <v>-700</v>
       </c>
       <c r="Z89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,31 +8144,32 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8022,8 +8243,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,28 +8445,31 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-5000</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>4</v>
@@ -8247,8 +8477,8 @@
       <c r="K94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -8316,8 +8546,11 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,31 +8585,32 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,94 +8987,97 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-10700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7000</v>
       </c>
-      <c r="F100" s="3">
-        <v>7000</v>
-      </c>
       <c r="G100" s="3">
+        <v>700</v>
+      </c>
+      <c r="H100" s="3">
         <v>6300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>87400</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>2800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>600</v>
-      </c>
-      <c r="X100" s="3">
-        <v>500</v>
       </c>
       <c r="Y100" s="3">
         <v>500</v>
       </c>
       <c r="Z100" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>1400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>900</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
         <v>0</v>
       </c>
       <c r="AE100" s="3">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="AF100" s="3">
         <v>1800</v>
@@ -8840,10 +9086,13 @@
         <v>1800</v>
       </c>
       <c r="AH100" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AI100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,70 +9189,73 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-12200</v>
       </c>
-      <c r="F102" s="3">
-        <v>5400</v>
-      </c>
       <c r="G102" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H102" s="3">
         <v>6600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>86000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-300</v>
-      </c>
-      <c r="W102" s="3">
-        <v>-200</v>
       </c>
       <c r="X102" s="3">
         <v>-200</v>
@@ -9012,30 +9264,33 @@
         <v>-200</v>
       </c>
       <c r="Z102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PMCB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PMCB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
   <si>
     <t>PMCB</t>
   </si>
@@ -656,151 +656,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F7" s="2">
         <v>45504</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45412</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45322</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45230</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45138</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45046</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44957</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44865</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44773</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44592</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44500</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44316</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44227</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44135</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44043</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43951</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43861</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43769</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43677</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43585</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43496</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43404</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43312</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43220</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43131</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43039</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42947</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42855</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42766</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -825,11 +833,11 @@
       <c r="J8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -900,8 +908,14 @@
       <c r="AI8" s="3">
         <v>0</v>
       </c>
+      <c r="AJ8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1001,8 +1015,14 @@
       <c r="AI9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1102,8 +1122,14 @@
       <c r="AI10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,8 +1165,10 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1163,46 +1191,46 @@
         <v>100</v>
       </c>
       <c r="J12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K12" s="3">
+        <v>100</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3">
         <v>200</v>
-      </c>
-      <c r="L12" s="3">
-        <v>200</v>
-      </c>
-      <c r="M12" s="3">
-        <v>300</v>
       </c>
       <c r="N12" s="3">
         <v>200</v>
       </c>
       <c r="O12" s="3">
+        <v>300</v>
+      </c>
+      <c r="P12" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q12" s="3">
         <v>100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>100</v>
-      </c>
-      <c r="V12" s="3">
-        <v>100</v>
-      </c>
-      <c r="W12" s="3">
-        <v>0</v>
       </c>
       <c r="X12" s="3">
         <v>100</v>
@@ -1214,34 +1242,40 @@
         <v>100</v>
       </c>
       <c r="AA12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="3">
         <v>100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD12" s="3">
         <v>300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,23 +1375,29 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E14" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F14" s="3">
         <v>-22100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>2000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1373,27 +1413,27 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3">
         <v>-100</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1406,11 +1446,11 @@
       <c r="W14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1442,8 +1482,14 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1543,8 +1589,14 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1629,224 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F17" s="3">
         <v>1300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>900</v>
-      </c>
-      <c r="O17" s="3">
-        <v>1000</v>
-      </c>
-      <c r="P17" s="3">
-        <v>1000</v>
       </c>
       <c r="Q17" s="3">
         <v>1000</v>
       </c>
       <c r="R17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T17" s="3">
         <v>800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>900</v>
-      </c>
-      <c r="T17" s="3">
-        <v>900</v>
-      </c>
-      <c r="U17" s="3">
-        <v>700</v>
       </c>
       <c r="V17" s="3">
         <v>900</v>
       </c>
       <c r="W17" s="3">
+        <v>700</v>
+      </c>
+      <c r="X17" s="3">
+        <v>900</v>
+      </c>
+      <c r="Y17" s="3">
         <v>1100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>1000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>1200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>1400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>2000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>1800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>1700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>1200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>1300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-2100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-2300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-1700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-1500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-900</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-1000</v>
       </c>
       <c r="Q18" s="3">
         <v>-1000</v>
       </c>
       <c r="R18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="S18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="T18" s="3">
         <v>-800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-900</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-900</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-700</v>
       </c>
       <c r="V18" s="3">
         <v>-900</v>
       </c>
       <c r="W18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="X18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-1100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,47 +1882,49 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F20" s="3">
         <v>-2000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-3800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-3300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>2000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1897,14 +1965,14 @@
         <v>0</v>
       </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
@@ -1917,50 +1985,56 @@
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F21" s="3">
         <v>800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>2600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>1900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-4100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-1900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-1500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-1400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-800</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2018,8 +2092,14 @@
       <c r="AI21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2044,11 +2124,11 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2077,11 +2157,11 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W22" s="3" t="s">
-        <v>4</v>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>4</v>
@@ -2098,11 +2178,11 @@
       <c r="AB22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE22" s="3">
         <v>0</v>
@@ -2119,109 +2199,121 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F23" s="3">
         <v>23400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>1300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>2800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-3200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-1900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-1500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-800</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-1000</v>
       </c>
       <c r="Q23" s="3">
         <v>-1000</v>
       </c>
       <c r="R23" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="S23" s="3">
         <v>-1000</v>
       </c>
       <c r="T23" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="U23" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="V23" s="3">
         <v>-900</v>
       </c>
       <c r="W23" s="3">
-        <v>-1100</v>
+        <v>-800</v>
       </c>
       <c r="X23" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="Y23" s="3">
         <v>-1100</v>
       </c>
       <c r="Z23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AB23" s="3">
         <v>-700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>-1300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2246,11 +2338,11 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2321,8 +2413,14 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2520,228 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F26" s="3">
         <v>23400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>2800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-3200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-1500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-800</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-1000</v>
       </c>
       <c r="Q26" s="3">
         <v>-1000</v>
       </c>
       <c r="R26" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="S26" s="3">
         <v>-1000</v>
       </c>
       <c r="T26" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="U26" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="V26" s="3">
         <v>-900</v>
       </c>
       <c r="W26" s="3">
-        <v>-1100</v>
+        <v>-800</v>
       </c>
       <c r="X26" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="Y26" s="3">
         <v>-1100</v>
       </c>
       <c r="Z26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AB26" s="3">
         <v>-700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-1300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>15000</v>
+        <v>-3000</v>
       </c>
       <c r="E27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F27" s="3">
+        <v>17200</v>
+      </c>
+      <c r="G27" s="3">
         <v>-2500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-5600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-2300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-6800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-800</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-1000</v>
       </c>
       <c r="Q27" s="3">
         <v>-1000</v>
       </c>
       <c r="R27" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="S27" s="3">
         <v>-1000</v>
       </c>
       <c r="T27" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="U27" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="V27" s="3">
         <v>-900</v>
       </c>
       <c r="W27" s="3">
-        <v>-1100</v>
+        <v>-800</v>
       </c>
       <c r="X27" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="Y27" s="3">
         <v>-1100</v>
       </c>
       <c r="Z27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2841,14 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2948,14 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +3055,14 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,47 +3162,53 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E32" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F32" s="3">
         <v>2000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>3800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>3300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-2000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -3109,14 +3249,14 @@
         <v>0</v>
       </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
@@ -3129,109 +3269,121 @@
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F33" s="3">
         <v>23400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>1300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>2800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-3200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-800</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-1000</v>
       </c>
       <c r="Q33" s="3">
         <v>-1000</v>
       </c>
       <c r="R33" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="S33" s="3">
         <v>-1000</v>
       </c>
       <c r="T33" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="U33" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="V33" s="3">
         <v>-900</v>
       </c>
       <c r="W33" s="3">
-        <v>-1100</v>
+        <v>-800</v>
       </c>
       <c r="X33" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="Y33" s="3">
         <v>-1100</v>
       </c>
       <c r="Z33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AA33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AB33" s="3">
         <v>-700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3483,233 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F35" s="3">
         <v>23400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>1300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>2800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-3200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-800</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-1000</v>
       </c>
       <c r="Q35" s="3">
         <v>-1000</v>
       </c>
       <c r="R35" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="S35" s="3">
         <v>-1000</v>
       </c>
       <c r="T35" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="U35" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="V35" s="3">
         <v>-900</v>
       </c>
       <c r="W35" s="3">
-        <v>-1100</v>
+        <v>-800</v>
       </c>
       <c r="X35" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="Y35" s="3">
         <v>-1100</v>
       </c>
       <c r="Z35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AA35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AB35" s="3">
         <v>-700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F38" s="2">
         <v>45504</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45412</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45322</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45230</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45138</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45046</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44957</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44865</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44773</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44592</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44500</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44316</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44227</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44135</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44043</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43951</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43861</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43769</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43677</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43585</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43496</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43404</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43312</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43220</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43131</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43039</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42947</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42855</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42766</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3745,10 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,114 +3784,122 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>20800</v>
+      </c>
+      <c r="F41" s="3">
         <v>32600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>50200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>61200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>73400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>74700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>68000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>72600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>77000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>82200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>85400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>86600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>86900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>3100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>3700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>2200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>100</v>
       </c>
-      <c r="W41" s="3">
-        <v>0</v>
-      </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="3">
         <v>300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>1800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>1100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>1500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>2700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>4300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>3500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>2500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -3814,8 +3994,14 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3840,11 +4026,11 @@
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -3915,8 +4101,14 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3941,11 +4133,11 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4016,8 +4208,14 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4042,35 +4240,35 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>500</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>100</v>
-      </c>
-      <c r="R45" s="3">
-        <v>0</v>
       </c>
       <c r="S45" s="3">
         <v>100</v>
       </c>
       <c r="T45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U45" s="3">
         <v>100</v>
@@ -4079,31 +4277,31 @@
         <v>100</v>
       </c>
       <c r="W45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X45" s="3">
         <v>100</v>
       </c>
       <c r="Y45" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z45" s="3">
         <v>100</v>
       </c>
-      <c r="Z45" s="3">
-        <v>0</v>
-      </c>
       <c r="AA45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC45" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AD45" s="3">
         <v>100</v>
       </c>
       <c r="AE45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AF45" s="3">
         <v>100</v>
@@ -4112,128 +4310,140 @@
         <v>100</v>
       </c>
       <c r="AH45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AI45" s="3">
         <v>100</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK45" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>21300</v>
+      </c>
+      <c r="F46" s="3">
         <v>32900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>50400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>61500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>73700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>74800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>68100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>72800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>77200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>82300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>85500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>86800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>87200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>3100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>3800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>2300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>2000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>1300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>1600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>2800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>4400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>3500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>2500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>24900</v>
+      </c>
+      <c r="F47" s="3">
         <v>29100</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F47" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G47" s="3">
-        <v>1600</v>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H47" s="3">
         <v>1600</v>
@@ -4319,8 +4529,14 @@
       <c r="AI47" s="3">
         <v>1600</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AK47" s="3">
+        <v>1600</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4345,11 +4561,11 @@
       <c r="J48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
-      </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -4420,8 +4636,14 @@
       <c r="AI48" s="3">
         <v>0</v>
       </c>
+      <c r="AJ48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4432,10 +4654,10 @@
         <v>1500</v>
       </c>
       <c r="F49" s="3">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="G49" s="3">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="H49" s="3">
         <v>3500</v>
@@ -4521,8 +4743,14 @@
       <c r="AI49" s="3">
         <v>3500</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AK49" s="3">
+        <v>3500</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4850,14 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,26 +4957,32 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F52" s="3">
         <v>6600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>7900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>4700</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
       <c r="I52" s="3">
         <v>0</v>
       </c>
@@ -4824,8 +5064,14 @@
       <c r="AI52" s="3">
         <v>0</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5171,121 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>43800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>55100</v>
+      </c>
+      <c r="F54" s="3">
         <v>70200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>59900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>71400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>78900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>79900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>73300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>78000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>82300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>87400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>90600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>91900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>92300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>6600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>7400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>8300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>8900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>7400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>6200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>5300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>5300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>5600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>5800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>5800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>6100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>7100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>6400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>6700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>7900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>9500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>8700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>7600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5321,10 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,109 +5360,117 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>300</v>
+      </c>
+      <c r="F57" s="3">
         <v>600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>500</v>
-      </c>
-      <c r="G57" s="3">
-        <v>100</v>
-      </c>
-      <c r="H57" s="3">
-        <v>700</v>
       </c>
       <c r="I57" s="3">
         <v>100</v>
       </c>
       <c r="J57" s="3">
+        <v>700</v>
+      </c>
+      <c r="K57" s="3">
+        <v>100</v>
+      </c>
+      <c r="L57" s="3">
         <v>400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>600</v>
-      </c>
-      <c r="M57" s="3">
-        <v>200</v>
-      </c>
-      <c r="N57" s="3">
-        <v>100</v>
       </c>
       <c r="O57" s="3">
         <v>200</v>
       </c>
       <c r="P57" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="Q57" s="3">
         <v>200</v>
       </c>
       <c r="R57" s="3">
+        <v>400</v>
+      </c>
+      <c r="S57" s="3">
+        <v>200</v>
+      </c>
+      <c r="T57" s="3">
         <v>100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>400</v>
-      </c>
-      <c r="U57" s="3">
-        <v>200</v>
-      </c>
-      <c r="V57" s="3">
-        <v>300</v>
       </c>
       <c r="W57" s="3">
         <v>200</v>
       </c>
       <c r="X57" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Y57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z57" s="3">
         <v>100</v>
       </c>
       <c r="AA57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC57" s="3">
         <v>300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5249,22 +5517,22 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>100</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W58" s="3" t="s">
-        <v>4</v>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
+        <v>0</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>4</v>
@@ -5278,11 +5546,11 @@
       <c r="AA58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>0</v>
+      <c r="AB58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD58" s="3">
         <v>0</v>
@@ -5302,82 +5570,88 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F59" s="3">
         <v>6200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>300</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
         <v>400</v>
-      </c>
-      <c r="L59" s="3">
-        <v>500</v>
-      </c>
-      <c r="M59" s="3">
-        <v>500</v>
       </c>
       <c r="N59" s="3">
         <v>500</v>
       </c>
       <c r="O59" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="P59" s="3">
         <v>500</v>
       </c>
       <c r="Q59" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="R59" s="3">
         <v>500</v>
       </c>
       <c r="S59" s="3">
+        <v>600</v>
+      </c>
+      <c r="T59" s="3">
         <v>500</v>
       </c>
-      <c r="T59" s="3">
-        <v>700</v>
-      </c>
       <c r="U59" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="V59" s="3">
         <v>700</v>
       </c>
       <c r="W59" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="X59" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="Y59" s="3">
         <v>600</v>
       </c>
       <c r="Z59" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AA59" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="AB59" s="3">
         <v>300</v>
@@ -5386,105 +5660,111 @@
         <v>300</v>
       </c>
       <c r="AD59" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="AE59" s="3">
         <v>300</v>
       </c>
       <c r="AF59" s="3">
+        <v>600</v>
+      </c>
+      <c r="AG59" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH59" s="3">
         <v>200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F60" s="3">
         <v>7500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>600</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>700</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>500</v>
       </c>
       <c r="AA60" s="3">
         <v>700</v>
       </c>
       <c r="AB60" s="3">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AC60" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="AD60" s="3">
         <v>900</v>
@@ -5499,13 +5779,19 @@
         <v>600</v>
       </c>
       <c r="AH60" s="3">
+        <v>900</v>
+      </c>
+      <c r="AI60" s="3">
         <v>600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
+        <v>600</v>
+      </c>
+      <c r="AK60" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5605,32 +5891,38 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F62" s="3">
         <v>9700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>13000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>14900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>15600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>18900</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
@@ -5643,11 +5935,11 @@
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
@@ -5706,8 +5998,14 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +6105,14 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6212,14 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,88 +6319,94 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>17200</v>
+        <v>3600</v>
       </c>
       <c r="E66" s="3">
-        <v>14600</v>
+        <v>11600</v>
       </c>
       <c r="F66" s="3">
         <v>17200</v>
       </c>
       <c r="G66" s="3">
+        <v>14600</v>
+      </c>
+      <c r="H66" s="3">
+        <v>17200</v>
+      </c>
+      <c r="I66" s="3">
         <v>17300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>20400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>900</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>700</v>
-      </c>
-      <c r="R66" s="3">
-        <v>600</v>
       </c>
       <c r="S66" s="3">
         <v>700</v>
       </c>
       <c r="T66" s="3">
+        <v>600</v>
+      </c>
+      <c r="U66" s="3">
+        <v>700</v>
+      </c>
+      <c r="V66" s="3">
         <v>1200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>600</v>
-      </c>
-      <c r="Y66" s="3">
-        <v>700</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>500</v>
       </c>
       <c r="AA66" s="3">
         <v>700</v>
       </c>
       <c r="AB66" s="3">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AC66" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="AD66" s="3">
         <v>900</v>
@@ -6105,13 +6421,19 @@
         <v>600</v>
       </c>
       <c r="AH66" s="3">
+        <v>900</v>
+      </c>
+      <c r="AI66" s="3">
         <v>600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
+        <v>600</v>
+      </c>
+      <c r="AK66" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6469,10 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6572,14 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,32 +6679,38 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3">
         <v>5300</v>
       </c>
-      <c r="E70" s="3">
+      <c r="G70" s="3">
         <v>17700</v>
       </c>
-      <c r="F70" s="3">
+      <c r="H70" s="3">
         <v>22800</v>
       </c>
-      <c r="G70" s="3">
+      <c r="I70" s="3">
         <v>24800</v>
       </c>
-      <c r="H70" s="3">
+      <c r="J70" s="3">
         <v>16800</v>
       </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3">
-        <v>0</v>
-      </c>
       <c r="K70" s="3">
         <v>0</v>
       </c>
@@ -6450,8 +6786,14 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6893,121 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-96700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-93700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-92200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-115600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-117000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-116400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-119500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-116000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-115800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-115100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-113200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-111600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-110200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-109400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-108400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-107400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-106400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-105700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-104700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-103900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-103100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-102200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-101200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-100000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-98900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-98200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-97200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-96000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-94700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-92600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-90800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-89100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>-88000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>-86700</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +7107,14 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7214,14 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7321,121 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>43500</v>
+      </c>
+      <c r="F76" s="3">
         <v>47700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>27600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>31400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>36800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>42700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>72700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>77100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>81000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>86300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>89900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>91300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>92100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>5700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>6700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>7600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>8300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>6200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>5100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>4300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>4500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>5000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>5000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>5400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>5400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>6200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>5800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>5800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>7300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>8700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>8100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>7000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7535,233 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F80" s="2">
         <v>45504</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45412</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45322</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45230</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45138</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45046</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44957</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44865</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44773</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44592</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44500</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44316</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44227</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44135</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44043</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43951</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43861</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43769</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43677</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43585</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43496</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43404</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43312</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43220</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43131</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43039</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42947</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42855</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42766</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F81" s="3">
         <v>23400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>1300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>2800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-3200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-800</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-1000</v>
       </c>
       <c r="Q81" s="3">
         <v>-1000</v>
       </c>
       <c r="R81" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="S81" s="3">
         <v>-1000</v>
       </c>
       <c r="T81" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="U81" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="V81" s="3">
         <v>-900</v>
       </c>
       <c r="W81" s="3">
-        <v>-1100</v>
+        <v>-800</v>
       </c>
       <c r="X81" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="Y81" s="3">
         <v>-1100</v>
       </c>
       <c r="Z81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AA81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AB81" s="3">
         <v>-700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,8 +7797,10 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7427,11 +7825,11 @@
       <c r="J83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -7502,8 +7900,14 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +8007,14 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +8114,14 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8221,14 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8328,14 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8435,121 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-2000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-1400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-900</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-600</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-1300</v>
       </c>
       <c r="T89" s="3">
         <v>-600</v>
       </c>
       <c r="U89" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="V89" s="3">
         <v>-600</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-400</v>
       </c>
       <c r="W89" s="3">
         <v>-600</v>
       </c>
       <c r="X89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Y89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-1600</v>
-      </c>
-      <c r="AF89" s="3">
-        <v>-900</v>
-      </c>
-      <c r="AG89" s="3">
-        <v>-800</v>
       </c>
       <c r="AH89" s="3">
         <v>-900</v>
       </c>
       <c r="AI89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AJ89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AK89" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,8 +8585,10 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8171,11 +8613,11 @@
       <c r="J91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -8246,8 +8688,14 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8795,14 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,26 +8902,32 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-7000</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-5000</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I94" s="3" t="s">
         <v>4</v>
       </c>
@@ -8480,11 +8940,11 @@
       <c r="L94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
@@ -8549,8 +9009,14 @@
       <c r="AI94" s="3">
         <v>0</v>
       </c>
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,8 +9052,10 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8612,11 +9080,11 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8687,8 +9155,14 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9262,14 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9369,14 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,109 +9476,121 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-10200</v>
+        <v>-3900</v>
       </c>
       <c r="E100" s="3">
         <v>-10700</v>
       </c>
       <c r="F100" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="H100" s="3">
         <v>-7000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>6300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-4300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-3800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-3400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-2100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>87400</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>2800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>1800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>1400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>500</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>1400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>900</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
       <c r="AF100" s="3">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="AG100" s="3">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="AH100" s="3">
         <v>1800</v>
       </c>
       <c r="AI100" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AJ100" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AK100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9192,105 +9690,117 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="F102" s="3">
         <v>-17500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-11000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-12200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>6600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-4600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-4300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-5300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-3200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>86000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>1600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>1300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-300</v>
-      </c>
-      <c r="X102" s="3">
-        <v>-200</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>-200</v>
       </c>
       <c r="Z102" s="3">
         <v>-200</v>
       </c>
       <c r="AA102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AB102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>1000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PMCB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PMCB_QTR_FIN.xlsx
@@ -2642,7 +2642,7 @@
         <v>-3000</v>
       </c>
       <c r="E27" s="3">
-        <v>-3000</v>
+        <v>-1600</v>
       </c>
       <c r="F27" s="3">
         <v>17200</v>

--- a/AAII_Financials/Quarterly/PMCB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PMCB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
   <si>
     <t>PMCB</t>
   </si>
@@ -656,159 +656,162 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E7" s="2">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45596</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45504</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45412</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45322</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45230</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45138</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45046</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44957</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44865</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44773</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44592</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44500</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44408</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44316</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44227</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44135</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44043</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43951</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43861</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43769</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43677</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43585</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43496</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43404</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43312</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43220</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43131</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43039</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42947</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42766</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -839,8 +842,8 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -914,8 +917,11 @@
       <c r="AK8" s="3">
         <v>0</v>
       </c>
+      <c r="AL8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1021,8 +1027,11 @@
       <c r="AK9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1128,8 +1137,11 @@
       <c r="AK10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1167,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1197,85 +1210,88 @@
         <v>100</v>
       </c>
       <c r="L12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M12" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N12" s="3">
         <v>200</v>
       </c>
       <c r="O12" s="3">
+        <v>200</v>
+      </c>
+      <c r="P12" s="3">
         <v>300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>200</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>100</v>
       </c>
       <c r="R12" s="3">
         <v>100</v>
       </c>
       <c r="S12" s="3">
+        <v>100</v>
+      </c>
+      <c r="T12" s="3">
         <v>300</v>
-      </c>
-      <c r="T12" s="3">
-        <v>200</v>
       </c>
       <c r="U12" s="3">
         <v>200</v>
       </c>
       <c r="V12" s="3">
+        <v>200</v>
+      </c>
+      <c r="W12" s="3">
         <v>300</v>
-      </c>
-      <c r="W12" s="3">
-        <v>100</v>
       </c>
       <c r="X12" s="3">
         <v>100</v>
       </c>
       <c r="Y12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="3">
         <v>100</v>
       </c>
-      <c r="AA12" s="3">
-        <v>0</v>
-      </c>
       <c r="AB12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC12" s="3">
         <v>100</v>
       </c>
       <c r="AD12" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AE12" s="3">
         <v>300</v>
       </c>
       <c r="AF12" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG12" s="3">
         <v>800</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>400</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>600</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1381,26 +1397,29 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="E14" s="3">
         <v>6200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-22100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1419,11 +1438,11 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>4</v>
@@ -1431,12 +1450,12 @@
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T14" s="3">
         <v>-100</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1452,8 +1471,8 @@
       <c r="Y14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1488,8 +1507,11 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1595,8 +1617,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,8 +1656,9 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1640,43 +1666,43 @@
         <v>1000</v>
       </c>
       <c r="E17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F17" s="3">
         <v>1100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>900</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>1000</v>
       </c>
       <c r="R17" s="3">
         <v>1000</v>
@@ -1685,61 +1711,64 @@
         <v>1000</v>
       </c>
       <c r="T17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U17" s="3">
         <v>800</v>
-      </c>
-      <c r="U17" s="3">
-        <v>900</v>
       </c>
       <c r="V17" s="3">
         <v>900</v>
       </c>
       <c r="W17" s="3">
+        <v>900</v>
+      </c>
+      <c r="X17" s="3">
         <v>700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>900</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>1100</v>
       </c>
       <c r="Z17" s="3">
         <v>1100</v>
       </c>
       <c r="AA17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB17" s="3">
         <v>1200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1747,43 +1776,43 @@
         <v>-1000</v>
       </c>
       <c r="E18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-900</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-1000</v>
       </c>
       <c r="R18" s="3">
         <v>-1000</v>
@@ -1792,61 +1821,64 @@
         <v>-1000</v>
       </c>
       <c r="T18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U18" s="3">
         <v>-800</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-900</v>
       </c>
       <c r="V18" s="3">
         <v>-900</v>
       </c>
       <c r="W18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="X18" s="3">
         <v>-700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-900</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-1100</v>
       </c>
       <c r="Z18" s="3">
         <v>-1100</v>
       </c>
       <c r="AA18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1884,49 +1916,50 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
-      </c>
-      <c r="N20" s="3">
-        <v>100</v>
       </c>
       <c r="O20" s="3">
         <v>100</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -1971,11 +2004,11 @@
         <v>0</v>
       </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>200</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
         <v>0</v>
       </c>
@@ -1991,53 +2024,56 @@
       <c r="AK20" s="3">
         <v>0</v>
       </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E21" s="3">
         <v>2900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-4100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-800</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2098,8 +2134,11 @@
       <c r="AK21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2130,8 +2169,8 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2163,8 +2202,8 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>4</v>
+      <c r="X22" s="3">
+        <v>0</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>4</v>
@@ -2184,8 +2223,8 @@
       <c r="AD22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE22" s="3">
-        <v>0</v>
+      <c r="AE22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF22" s="3">
         <v>0</v>
@@ -2205,52 +2244,55 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>23400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-800</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-1000</v>
       </c>
       <c r="R23" s="3">
         <v>-1000</v>
@@ -2259,22 +2301,22 @@
         <v>-1000</v>
       </c>
       <c r="T23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U23" s="3">
         <v>-800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-900</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-1100</v>
       </c>
       <c r="Z23" s="3">
         <v>-1100</v>
@@ -2283,37 +2325,40 @@
         <v>-1100</v>
       </c>
       <c r="AB23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AC23" s="3">
         <v>-700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-1300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2344,8 +2389,8 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -2419,8 +2464,11 @@
       <c r="AK24" s="3">
         <v>0</v>
       </c>
+      <c r="AL24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2526,52 +2574,55 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>23400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-800</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-1000</v>
       </c>
       <c r="R26" s="3">
         <v>-1000</v>
@@ -2580,22 +2631,22 @@
         <v>-1000</v>
       </c>
       <c r="T26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U26" s="3">
         <v>-800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-900</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-1100</v>
       </c>
       <c r="Z26" s="3">
         <v>-1100</v>
@@ -2604,81 +2655,84 @@
         <v>-1100</v>
       </c>
       <c r="AB26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-1300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>17200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-800</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-1000</v>
       </c>
       <c r="R27" s="3">
         <v>-1000</v>
@@ -2687,22 +2741,22 @@
         <v>-1000</v>
       </c>
       <c r="T27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U27" s="3">
         <v>-800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-900</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>-1100</v>
       </c>
       <c r="Z27" s="3">
         <v>-1100</v>
@@ -2711,37 +2765,40 @@
         <v>-1100</v>
       </c>
       <c r="AB27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2847,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2954,8 +3014,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,49 +3234,52 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="3">
         <v>3800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-100</v>
       </c>
       <c r="O32" s="3">
         <v>-100</v>
       </c>
       <c r="P32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -3255,11 +3324,11 @@
         <v>0</v>
       </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-200</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
         <v>0</v>
       </c>
@@ -3275,52 +3344,55 @@
       <c r="AK32" s="3">
         <v>0</v>
       </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>23400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-800</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-1000</v>
       </c>
       <c r="R33" s="3">
         <v>-1000</v>
@@ -3329,22 +3401,22 @@
         <v>-1000</v>
       </c>
       <c r="T33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U33" s="3">
         <v>-800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-900</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>-1100</v>
       </c>
       <c r="Z33" s="3">
         <v>-1100</v>
@@ -3353,37 +3425,40 @@
         <v>-1100</v>
       </c>
       <c r="AB33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,52 +3564,55 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>23400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-800</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-1000</v>
       </c>
       <c r="R35" s="3">
         <v>-1000</v>
@@ -3543,22 +3621,22 @@
         <v>-1000</v>
       </c>
       <c r="T35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U35" s="3">
         <v>-800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-900</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>-1100</v>
       </c>
       <c r="Z35" s="3">
         <v>-1100</v>
@@ -3567,149 +3645,155 @@
         <v>-1100</v>
       </c>
       <c r="AB35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E38" s="2">
         <v>45688</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45596</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45504</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45412</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45322</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45230</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45138</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45046</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44957</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44865</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44773</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44592</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44500</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44408</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44316</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44227</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44135</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44043</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43951</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43861</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43769</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43677</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43585</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43496</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43404</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43312</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43220</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43131</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43039</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42947</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42766</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,115 +3871,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E41" s="3">
         <v>16400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>20800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>32600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>50200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>61200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>73400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>74700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>68000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>72600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>77000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>82200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>85400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>86600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>86900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>100</v>
       </c>
-      <c r="Y41" s="3">
-        <v>0</v>
-      </c>
       <c r="Z41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="3">
         <v>300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3902,7 +3991,7 @@
         <v>400</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -4000,13 +4089,16 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>4</v>
+      <c r="D43" s="3">
+        <v>3700</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>4</v>
@@ -4032,8 +4124,8 @@
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -4107,8 +4199,11 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4139,8 +4234,8 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4214,13 +4309,16 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
+      <c r="D45" s="3">
+        <v>2900</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>4</v>
@@ -4246,32 +4344,32 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
       <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3">
         <v>100</v>
-      </c>
-      <c r="P45" s="3">
-        <v>200</v>
       </c>
       <c r="Q45" s="3">
         <v>200</v>
       </c>
       <c r="R45" s="3">
+        <v>200</v>
+      </c>
+      <c r="S45" s="3">
         <v>500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3">
-        <v>0</v>
-      </c>
       <c r="U45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V45" s="3">
         <v>100</v>
@@ -4283,28 +4381,28 @@
         <v>100</v>
       </c>
       <c r="Y45" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z45" s="3">
         <v>200</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>100</v>
       </c>
       <c r="AA45" s="3">
         <v>100</v>
       </c>
       <c r="AB45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC45" s="3">
         <v>0</v>
       </c>
       <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="3">
         <v>100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>200</v>
-      </c>
-      <c r="AF45" s="3">
-        <v>100</v>
       </c>
       <c r="AG45" s="3">
         <v>100</v>
@@ -4316,137 +4414,143 @@
         <v>100</v>
       </c>
       <c r="AJ45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E46" s="3">
         <v>17000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>21300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>32900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>50400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>61500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>73700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>74800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>68100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>72800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>77200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>82300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>85500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>86800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>87200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1000</v>
-      </c>
-      <c r="X46" s="3">
-        <v>200</v>
       </c>
       <c r="Y46" s="3">
         <v>200</v>
       </c>
       <c r="Z46" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA46" s="3">
         <v>500</v>
-      </c>
-      <c r="AA46" s="3">
-        <v>700</v>
       </c>
       <c r="AB46" s="3">
         <v>700</v>
       </c>
       <c r="AC46" s="3">
+        <v>700</v>
+      </c>
+      <c r="AD46" s="3">
         <v>900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E47" s="3">
         <v>18600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>24900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>29100</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H47" s="3">
-        <v>1600</v>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I47" s="3">
         <v>1600</v>
@@ -4535,8 +4639,11 @@
       <c r="AK47" s="3">
         <v>1600</v>
       </c>
+      <c r="AL47" s="3">
+        <v>1600</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4567,8 +4674,8 @@
       <c r="L48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -4642,8 +4749,11 @@
       <c r="AK48" s="3">
         <v>0</v>
       </c>
+      <c r="AL48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4660,7 +4770,7 @@
         <v>1500</v>
       </c>
       <c r="H49" s="3">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="I49" s="3">
         <v>3500</v>
@@ -4749,8 +4859,11 @@
       <c r="AK49" s="3">
         <v>3500</v>
       </c>
+      <c r="AL49" s="3">
+        <v>3500</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,29 +5079,32 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E52" s="3">
         <v>6700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4700</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
       <c r="J52" s="3">
         <v>0</v>
       </c>
@@ -5070,8 +5189,11 @@
       <c r="AK52" s="3">
         <v>0</v>
       </c>
+      <c r="AL52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>55200</v>
+      </c>
+      <c r="E54" s="3">
         <v>43800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>55100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>70200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>59900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>71400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>78900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>79900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>73300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>78000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>82300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>87400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>90600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>91900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>92300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>8300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>8900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6200</v>
-      </c>
-      <c r="X54" s="3">
-        <v>5300</v>
       </c>
       <c r="Y54" s="3">
         <v>5300</v>
       </c>
       <c r="Z54" s="3">
+        <v>5300</v>
+      </c>
+      <c r="AA54" s="3">
         <v>5600</v>
-      </c>
-      <c r="AA54" s="3">
-        <v>5800</v>
       </c>
       <c r="AB54" s="3">
         <v>5800</v>
       </c>
       <c r="AC54" s="3">
+        <v>5800</v>
+      </c>
+      <c r="AD54" s="3">
         <v>6100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>9500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>8700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>7600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,79 +5491,80 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400</v>
+      </c>
+      <c r="E57" s="3">
         <v>500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>200</v>
-      </c>
-      <c r="T57" s="3">
-        <v>100</v>
       </c>
       <c r="U57" s="3">
         <v>100</v>
       </c>
       <c r="V57" s="3">
+        <v>100</v>
+      </c>
+      <c r="W57" s="3">
         <v>400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>200</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>100</v>
       </c>
       <c r="AA57" s="3">
         <v>100</v>
@@ -5443,34 +5573,37 @@
         <v>100</v>
       </c>
       <c r="AC57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD57" s="3">
         <v>300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>400</v>
-      </c>
-      <c r="AF57" s="3">
-        <v>300</v>
       </c>
       <c r="AG57" s="3">
         <v>300</v>
       </c>
       <c r="AH57" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI57" s="3">
         <v>600</v>
-      </c>
-      <c r="AI57" s="3">
-        <v>400</v>
       </c>
       <c r="AJ57" s="3">
         <v>400</v>
       </c>
       <c r="AK57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AL57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5523,19 +5656,19 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U58" s="3">
         <v>100</v>
       </c>
       <c r="V58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>4</v>
+      <c r="X58" s="3">
+        <v>0</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>4</v>
@@ -5552,8 +5685,8 @@
       <c r="AC58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD58" s="3">
-        <v>0</v>
+      <c r="AD58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE58" s="3">
         <v>0</v>
@@ -5576,43 +5709,46 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E59" s="3">
+      <c r="D59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3">
         <v>3700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6200</v>
       </c>
-      <c r="G59" s="3">
-        <v>500</v>
-      </c>
       <c r="H59" s="3">
+        <v>6300</v>
+      </c>
+      <c r="I59" s="3">
         <v>1000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>300</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>400</v>
-      </c>
-      <c r="N59" s="3">
-        <v>500</v>
       </c>
       <c r="O59" s="3">
         <v>500</v>
@@ -5621,40 +5757,40 @@
         <v>500</v>
       </c>
       <c r="Q59" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="R59" s="3">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3">
         <v>500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>600</v>
-      </c>
-      <c r="T59" s="3">
-        <v>500</v>
       </c>
       <c r="U59" s="3">
         <v>500</v>
       </c>
       <c r="V59" s="3">
+        <v>500</v>
+      </c>
+      <c r="W59" s="3">
         <v>700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>600</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>300</v>
       </c>
       <c r="AC59" s="3">
         <v>300</v>
@@ -5666,132 +5802,138 @@
         <v>300</v>
       </c>
       <c r="AF59" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG59" s="3">
         <v>600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>300</v>
-      </c>
-      <c r="AH59" s="3">
-        <v>200</v>
       </c>
       <c r="AI59" s="3">
         <v>200</v>
       </c>
       <c r="AJ59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AK59" s="3">
         <v>100</v>
       </c>
+      <c r="AL59" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E60" s="3">
         <v>1200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7500</v>
       </c>
-      <c r="G60" s="3">
-        <v>1600</v>
-      </c>
       <c r="H60" s="3">
+        <v>7400</v>
+      </c>
+      <c r="I60" s="3">
         <v>2200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>700</v>
-      </c>
-      <c r="T60" s="3">
-        <v>600</v>
       </c>
       <c r="U60" s="3">
         <v>600</v>
       </c>
       <c r="V60" s="3">
+        <v>600</v>
+      </c>
+      <c r="W60" s="3">
         <v>1200</v>
-      </c>
-      <c r="W60" s="3">
-        <v>1000</v>
       </c>
       <c r="X60" s="3">
         <v>1000</v>
       </c>
       <c r="Y60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Z60" s="3">
         <v>800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>900</v>
-      </c>
-      <c r="AI60" s="3">
-        <v>600</v>
       </c>
       <c r="AJ60" s="3">
         <v>600</v>
       </c>
       <c r="AK60" s="3">
+        <v>600</v>
+      </c>
+      <c r="AL60" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5897,35 +6039,38 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>400</v>
+      </c>
+      <c r="E62" s="3">
         <v>2400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>14900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>15600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>18900</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
@@ -5941,8 +6086,8 @@
       <c r="P62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -6004,8 +6149,11 @@
       <c r="AK62" s="3">
         <v>0</v>
       </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6218,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E66" s="3">
         <v>3600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>17200</v>
       </c>
-      <c r="G66" s="3">
-        <v>14600</v>
-      </c>
       <c r="H66" s="3">
+        <v>20400</v>
+      </c>
+      <c r="I66" s="3">
         <v>17200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>17300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>20400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>900</v>
-      </c>
-      <c r="AI66" s="3">
-        <v>600</v>
       </c>
       <c r="AJ66" s="3">
         <v>600</v>
       </c>
       <c r="AK66" s="3">
+        <v>600</v>
+      </c>
+      <c r="AL66" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6697,23 +6864,23 @@
         <v>0</v>
       </c>
       <c r="F70" s="3">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3">
         <v>5300</v>
       </c>
-      <c r="G70" s="3">
-        <v>17700</v>
-      </c>
       <c r="H70" s="3">
+        <v>11900</v>
+      </c>
+      <c r="I70" s="3">
         <v>22800</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>24800</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>16800</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
       <c r="L70" s="3">
         <v>0</v>
       </c>
@@ -6792,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-85000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-96700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-93700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-92200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-115600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-117000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-116400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-119500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-116000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-115800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-115100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-113200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-111600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-110200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-109400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-108400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-107400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-106400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-105700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-104700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-103900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-103100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-102200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-101200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-100000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-98900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-98200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-97200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-96000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-94700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-92600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-90800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-89100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-88000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-86700</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>51900</v>
+      </c>
+      <c r="E76" s="3">
         <v>40300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>43500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>47700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>27600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>31400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>36800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>42700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>72700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>77100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>81000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>86300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>89900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>91300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>92100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4500</v>
-      </c>
-      <c r="Z76" s="3">
-        <v>5000</v>
       </c>
       <c r="AA76" s="3">
         <v>5000</v>
       </c>
       <c r="AB76" s="3">
-        <v>5400</v>
+        <v>5000</v>
       </c>
       <c r="AC76" s="3">
         <v>5400</v>
       </c>
       <c r="AD76" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AE76" s="3">
         <v>6200</v>
-      </c>
-      <c r="AE76" s="3">
-        <v>5800</v>
       </c>
       <c r="AF76" s="3">
         <v>5800</v>
       </c>
       <c r="AG76" s="3">
+        <v>5800</v>
+      </c>
+      <c r="AH76" s="3">
         <v>7300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>8700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>8100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>7000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,164 +7729,170 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E80" s="2">
         <v>45688</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45596</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45504</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45412</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45322</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45230</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45138</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45046</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44957</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44865</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44773</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44592</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44500</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44408</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44316</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44227</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44135</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44043</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43951</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43861</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43769</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43677</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43585</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43496</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43404</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43312</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43220</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43131</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43039</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42947</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42766</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>23400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-800</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-1000</v>
       </c>
       <c r="R81" s="3">
         <v>-1000</v>
@@ -7707,22 +7901,22 @@
         <v>-1000</v>
       </c>
       <c r="T81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U81" s="3">
         <v>-800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-900</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>-1100</v>
       </c>
       <c r="Z81" s="3">
         <v>-1100</v>
@@ -7731,37 +7925,40 @@
         <v>-1100</v>
       </c>
       <c r="AB81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,8 +7996,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7831,8 +8029,8 @@
       <c r="L83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -7906,8 +8104,11 @@
       <c r="AK83" s="3">
         <v>0</v>
       </c>
+      <c r="AL83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1300</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-600</v>
       </c>
       <c r="W89" s="3">
         <v>-600</v>
       </c>
       <c r="X89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-800</v>
-      </c>
-      <c r="AA89" s="3">
-        <v>-700</v>
       </c>
       <c r="AB89" s="3">
         <v>-700</v>
       </c>
       <c r="AC89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,8 +8806,9 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8619,8 +8839,8 @@
       <c r="L91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -8694,8 +8914,11 @@
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,8 +9134,11 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8920,17 +9149,17 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-7000</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-5000</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>4</v>
       </c>
@@ -8946,8 +9175,8 @@
       <c r="N94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
@@ -9015,8 +9244,11 @@
       <c r="AK94" s="3">
         <v>0</v>
       </c>
+      <c r="AL94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,8 +9286,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9086,8 +9319,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9161,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,103 +9724,106 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-10700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-10200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-10700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>87400</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>2800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>600</v>
-      </c>
-      <c r="AA100" s="3">
-        <v>500</v>
       </c>
       <c r="AB100" s="3">
         <v>500</v>
       </c>
       <c r="AC100" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>1400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>900</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
       <c r="AG100" s="3">
         <v>0</v>
       </c>
       <c r="AH100" s="3">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="AI100" s="3">
         <v>1800</v>
@@ -9587,10 +9832,13 @@
         <v>1800</v>
       </c>
       <c r="AK100" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AL100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9696,79 +9944,82 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-17500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-12200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>86000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-300</v>
-      </c>
-      <c r="Z102" s="3">
-        <v>-200</v>
       </c>
       <c r="AA102" s="3">
         <v>-200</v>
@@ -9777,30 +10028,33 @@
         <v>-200</v>
       </c>
       <c r="AC102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PMCB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PMCB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
   <si>
     <t>PMCB</t>
   </si>
@@ -656,166 +656,174 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F7" s="2">
         <v>45869</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45777</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45688</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45596</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45504</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45412</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45322</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45230</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45138</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45046</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44957</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44865</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44773</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44681</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44592</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44500</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44408</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44316</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44227</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44135</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44043</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43951</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43861</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43769</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43677</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43585</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43496</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43404</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43312</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43220</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43131</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42947</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42855</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42766</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -852,11 +860,11 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -927,8 +935,14 @@
       <c r="AM8" s="3">
         <v>0</v>
       </c>
+      <c r="AN8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1040,8 +1054,14 @@
       <c r="AM9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1173,14 @@
       <c r="AM10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1194,8 +1220,10 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1230,46 +1258,46 @@
         <v>100</v>
       </c>
       <c r="N12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O12" s="3">
+        <v>100</v>
+      </c>
+      <c r="P12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="3">
         <v>200</v>
-      </c>
-      <c r="P12" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>300</v>
       </c>
       <c r="R12" s="3">
         <v>200</v>
       </c>
       <c r="S12" s="3">
+        <v>300</v>
+      </c>
+      <c r="T12" s="3">
+        <v>200</v>
+      </c>
+      <c r="U12" s="3">
         <v>100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>100</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>0</v>
       </c>
       <c r="AB12" s="3">
         <v>100</v>
@@ -1281,34 +1309,40 @@
         <v>100</v>
       </c>
       <c r="AE12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="3">
         <v>100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH12" s="3">
         <v>300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>300</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>800</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>500</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>400</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AM12" s="3">
         <v>200</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AN12" s="3">
         <v>600</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AO12" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1420,35 +1454,41 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E14" s="3">
+        <v>300</v>
+      </c>
+      <c r="F14" s="3">
         <v>2900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-12800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>6200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>4300</v>
       </c>
-      <c r="H14" s="3">
-        <v>-22400</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="K14" s="3">
         <v>2000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1464,27 +1504,27 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W14" s="3">
         <v>-100</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1497,11 +1537,11 @@
       <c r="AA14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1533,8 +1573,14 @@
       <c r="AM14" s="3">
         <v>0</v>
       </c>
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1646,8 +1692,14 @@
       <c r="AM15" s="3">
         <v>0</v>
       </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1684,234 +1736,248 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F17" s="3">
         <v>800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>2300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>900</v>
-      </c>
-      <c r="S17" s="3">
-        <v>1000</v>
-      </c>
-      <c r="T17" s="3">
-        <v>1000</v>
       </c>
       <c r="U17" s="3">
         <v>1000</v>
       </c>
       <c r="V17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X17" s="3">
         <v>800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>900</v>
-      </c>
-      <c r="X17" s="3">
-        <v>900</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>700</v>
       </c>
       <c r="Z17" s="3">
         <v>900</v>
       </c>
       <c r="AA17" s="3">
+        <v>700</v>
+      </c>
+      <c r="AB17" s="3">
+        <v>900</v>
+      </c>
+      <c r="AC17" s="3">
         <v>1100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>1100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>1200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>1000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>1200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>1400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>2000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>1700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>1200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>1300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-1300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-1400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-2100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-1600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-2300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-1500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-900</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-1000</v>
       </c>
       <c r="U18" s="3">
         <v>-1000</v>
       </c>
       <c r="V18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="W18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="X18" s="3">
         <v>-800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-900</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-900</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-700</v>
       </c>
       <c r="Z18" s="3">
         <v>-900</v>
       </c>
       <c r="AA18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1951,59 +2017,61 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F20" s="3">
         <v>4800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-3800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-3500</v>
       </c>
-      <c r="H20" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K20" s="3">
         <v>-3800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-3300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>2000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -2044,14 +2112,14 @@
         <v>0</v>
       </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
         <v>200</v>
       </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI20" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
@@ -2064,62 +2132,68 @@
       <c r="AM20" s="3">
         <v>0</v>
       </c>
+      <c r="AN20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-5600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-1300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>2900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>2400</v>
       </c>
-      <c r="H21" s="3">
-        <v>500</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
+        <v>800</v>
+      </c>
+      <c r="K21" s="3">
         <v>2600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>1900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-4100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-1400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-1900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-1400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-800</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2177,8 +2251,14 @@
       <c r="AM21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2215,11 +2295,11 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2248,11 +2328,11 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA22" s="3" t="s">
-        <v>4</v>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>4</v>
@@ -2269,11 +2349,11 @@
       <c r="AF22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>0</v>
+      <c r="AG22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AI22" s="3">
         <v>0</v>
@@ -2290,121 +2370,133 @@
       <c r="AM22" s="3">
         <v>0</v>
       </c>
+      <c r="AN22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-8400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>11700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-3000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>23400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>2800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-3200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-1900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-1400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-800</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-1000</v>
       </c>
       <c r="U23" s="3">
         <v>-1000</v>
       </c>
       <c r="V23" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="W23" s="3">
         <v>-1000</v>
       </c>
       <c r="X23" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="Y23" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="Z23" s="3">
         <v>-900</v>
       </c>
       <c r="AA23" s="3">
-        <v>-1100</v>
+        <v>-800</v>
       </c>
       <c r="AB23" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="AC23" s="3">
         <v>-1100</v>
       </c>
       <c r="AD23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AE23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AF23" s="3">
         <v>-700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>-1300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2441,11 +2533,11 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2516,8 +2608,14 @@
       <c r="AM24" s="3">
         <v>0</v>
       </c>
+      <c r="AN24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2629,234 +2727,252 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-8400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>11700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-3000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>23400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>1300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>2800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-3200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-1900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-1400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-800</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-1000</v>
       </c>
       <c r="U26" s="3">
         <v>-1000</v>
       </c>
       <c r="V26" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="W26" s="3">
         <v>-1000</v>
       </c>
       <c r="X26" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="Y26" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="Z26" s="3">
         <v>-900</v>
       </c>
       <c r="AA26" s="3">
-        <v>-1100</v>
+        <v>-800</v>
       </c>
       <c r="AB26" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="AC26" s="3">
         <v>-1100</v>
       </c>
       <c r="AD26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AE26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AF26" s="3">
         <v>-700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>-1300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="G27" s="3">
         <v>10800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-3000</v>
       </c>
-      <c r="G27" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="H27" s="3">
-        <v>15000</v>
-      </c>
       <c r="I27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="J27" s="3">
+        <v>17200</v>
+      </c>
+      <c r="K27" s="3">
         <v>-2500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-5600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-2300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-6800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-1900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-1400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-800</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-1000</v>
       </c>
       <c r="U27" s="3">
         <v>-1000</v>
       </c>
       <c r="V27" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="W27" s="3">
         <v>-1000</v>
       </c>
       <c r="X27" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="Y27" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="Z27" s="3">
         <v>-900</v>
       </c>
       <c r="AA27" s="3">
-        <v>-1100</v>
+        <v>-800</v>
       </c>
       <c r="AB27" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="AC27" s="3">
         <v>-1100</v>
       </c>
       <c r="AD27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AE27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AF27" s="3">
         <v>-700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2968,8 +3084,14 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3081,8 +3203,14 @@
       <c r="AM29" s="3">
         <v>0</v>
       </c>
+      <c r="AN29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3194,8 +3322,14 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3307,59 +3441,65 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="F32" s="3">
         <v>-4800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>3800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>3500</v>
       </c>
-      <c r="H32" s="3">
-        <v>1800</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K32" s="3">
         <v>3800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>3300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-2000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -3400,14 +3540,14 @@
         <v>0</v>
       </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-200</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI32" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
@@ -3420,121 +3560,133 @@
       <c r="AM32" s="3">
         <v>0</v>
       </c>
+      <c r="AN32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-8400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>11700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-3000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>23400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>1300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>2800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-3200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-1900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-1400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-800</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-1000</v>
       </c>
       <c r="U33" s="3">
         <v>-1000</v>
       </c>
       <c r="V33" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="W33" s="3">
         <v>-1000</v>
       </c>
       <c r="X33" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="Y33" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="Z33" s="3">
         <v>-900</v>
       </c>
       <c r="AA33" s="3">
-        <v>-1100</v>
+        <v>-800</v>
       </c>
       <c r="AB33" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="AC33" s="3">
         <v>-1100</v>
       </c>
       <c r="AD33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AE33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AF33" s="3">
         <v>-700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3646,239 +3798,257 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-8400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>11700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-3000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>23400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>2800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-3200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-1900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-1400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-800</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-1000</v>
       </c>
       <c r="U35" s="3">
         <v>-1000</v>
       </c>
       <c r="V35" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="W35" s="3">
         <v>-1000</v>
       </c>
       <c r="X35" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="Y35" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="Z35" s="3">
         <v>-900</v>
       </c>
       <c r="AA35" s="3">
-        <v>-1100</v>
+        <v>-800</v>
       </c>
       <c r="AB35" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="AC35" s="3">
         <v>-1100</v>
       </c>
       <c r="AD35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AE35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AF35" s="3">
         <v>-700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F38" s="2">
         <v>45869</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45777</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45688</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45596</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45504</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45412</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45322</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45230</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45138</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45046</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44957</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44865</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44773</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44681</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44592</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44500</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44408</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44316</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44227</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44135</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44043</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43951</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43861</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43769</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43677</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43585</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43496</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43404</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43312</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43220</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43131</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42947</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42855</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42766</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3918,8 +4088,10 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3959,139 +4131,147 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>15400</v>
+      </c>
+      <c r="F41" s="3">
         <v>13200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>15200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>16400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>20800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>32600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>50200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>61200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>73400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>74700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>68000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>72600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>77000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>82200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>85400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>86600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>86900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>2200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>3100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>3700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>2200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>100</v>
       </c>
-      <c r="AA41" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="3">
         <v>300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>1800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>1100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>1500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>2700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>4300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>3500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>2500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E42" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F42" s="3">
+        <v>4900</v>
+      </c>
+      <c r="G42" s="3">
         <v>400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>400</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -4185,23 +4365,29 @@
       <c r="AM42" s="3">
         <v>0</v>
       </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>4600</v>
-      </c>
-      <c r="E43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3">
         <v>3700</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>4</v>
       </c>
@@ -4223,11 +4409,11 @@
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -4298,8 +4484,14 @@
       <c r="AM43" s="3">
         <v>0</v>
       </c>
+      <c r="AN43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4336,11 +4528,11 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4411,23 +4603,29 @@
       <c r="AM44" s="3">
         <v>0</v>
       </c>
+      <c r="AN44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F45" s="3">
         <v>800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>2900</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>4</v>
       </c>
@@ -4449,35 +4647,35 @@
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3">
         <v>100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>500</v>
-      </c>
-      <c r="U45" s="3">
-        <v>100</v>
-      </c>
-      <c r="V45" s="3">
-        <v>0</v>
       </c>
       <c r="W45" s="3">
         <v>100</v>
       </c>
       <c r="X45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="3">
         <v>100</v>
@@ -4486,31 +4684,31 @@
         <v>100</v>
       </c>
       <c r="AA45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB45" s="3">
         <v>100</v>
       </c>
       <c r="AC45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD45" s="3">
         <v>100</v>
       </c>
-      <c r="AD45" s="3">
-        <v>0</v>
-      </c>
       <c r="AE45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG45" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AH45" s="3">
         <v>100</v>
       </c>
       <c r="AI45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AJ45" s="3">
         <v>100</v>
@@ -4519,152 +4717,164 @@
         <v>100</v>
       </c>
       <c r="AL45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM45" s="3">
         <v>100</v>
       </c>
+      <c r="AN45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO45" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>23000</v>
+      </c>
+      <c r="F46" s="3">
         <v>19100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>22400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>17000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>21300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>32900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>50400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>61500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>73700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>74800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>68100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>72800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>77200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>82300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>85500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>86800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>87200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>2300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>3100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>3800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>2300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>2000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>1300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>1600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>4400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>3500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>2500</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E47" s="3">
+        <v>20700</v>
+      </c>
+      <c r="F47" s="3">
         <v>19600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>22500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>18600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>24900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>29100</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J47" s="3">
-        <v>1600</v>
-      </c>
-      <c r="K47" s="3">
-        <v>1600</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>1600</v>
@@ -4750,8 +4960,14 @@
       <c r="AM47" s="3">
         <v>1600</v>
       </c>
+      <c r="AN47" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AO47" s="3">
+        <v>1600</v>
+      </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4788,11 +5004,11 @@
       <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
-      </c>
-      <c r="P48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
@@ -4863,8 +5079,14 @@
       <c r="AM48" s="3">
         <v>0</v>
       </c>
+      <c r="AN48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4887,10 +5109,10 @@
         <v>1500</v>
       </c>
       <c r="J49" s="3">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="K49" s="3">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="L49" s="3">
         <v>3500</v>
@@ -4976,8 +5198,14 @@
       <c r="AM49" s="3">
         <v>3500</v>
       </c>
+      <c r="AN49" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AO49" s="3">
+        <v>3500</v>
+      </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5089,8 +5317,14 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5202,38 +5436,44 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>10700</v>
+      </c>
+      <c r="F52" s="3">
         <v>4800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>8800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>6700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>7400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>6600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>7900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>4700</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
@@ -5315,8 +5555,14 @@
       <c r="AM52" s="3">
         <v>0</v>
       </c>
+      <c r="AN52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5428,121 +5674,133 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>55900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>56000</v>
+      </c>
+      <c r="F54" s="3">
         <v>45100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>55200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>43800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>55100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>70200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>59900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>71400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>78900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>79900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>73300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>78000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>82300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>87400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>90600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>91900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>92300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>6600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>7400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>8300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>8900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>7400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>6200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>5300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>5300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>5600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>5800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>5800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>6100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>7100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>6400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>6700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>9500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>8700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>7600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5582,8 +5840,10 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5623,121 +5883,129 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="E57" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="F57" s="3">
         <v>500</v>
       </c>
       <c r="G57" s="3">
+        <v>400</v>
+      </c>
+      <c r="H57" s="3">
+        <v>500</v>
+      </c>
+      <c r="I57" s="3">
         <v>300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>500</v>
-      </c>
-      <c r="K57" s="3">
-        <v>100</v>
-      </c>
-      <c r="L57" s="3">
-        <v>700</v>
       </c>
       <c r="M57" s="3">
         <v>100</v>
       </c>
       <c r="N57" s="3">
+        <v>700</v>
+      </c>
+      <c r="O57" s="3">
+        <v>100</v>
+      </c>
+      <c r="P57" s="3">
         <v>400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>600</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>200</v>
-      </c>
-      <c r="R57" s="3">
-        <v>100</v>
       </c>
       <c r="S57" s="3">
         <v>200</v>
       </c>
       <c r="T57" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="U57" s="3">
         <v>200</v>
       </c>
       <c r="V57" s="3">
+        <v>400</v>
+      </c>
+      <c r="W57" s="3">
+        <v>200</v>
+      </c>
+      <c r="X57" s="3">
         <v>100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>400</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>200</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>300</v>
       </c>
       <c r="AA57" s="3">
         <v>200</v>
       </c>
       <c r="AB57" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AC57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD57" s="3">
         <v>100</v>
       </c>
       <c r="AE57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG57" s="3">
         <v>300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>400</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>400</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5796,22 +6064,22 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>100</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA58" s="3" t="s">
-        <v>4</v>
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
+        <v>0</v>
       </c>
       <c r="AB58" s="3" t="s">
         <v>4</v>
@@ -5825,11 +6093,11 @@
       <c r="AE58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG58" s="3">
-        <v>0</v>
+      <c r="AF58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH58" s="3">
         <v>0</v>
@@ -5849,94 +6117,100 @@
       <c r="AM58" s="3">
         <v>0</v>
       </c>
+      <c r="AN58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3">
+        <v>200</v>
+      </c>
+      <c r="F59" s="3">
         <v>300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2000</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3">
         <v>3700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>6200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>6300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>300</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q59" s="3">
         <v>400</v>
-      </c>
-      <c r="P59" s="3">
-        <v>500</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>500</v>
       </c>
       <c r="R59" s="3">
         <v>500</v>
       </c>
       <c r="S59" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="T59" s="3">
         <v>500</v>
       </c>
       <c r="U59" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="V59" s="3">
         <v>500</v>
       </c>
       <c r="W59" s="3">
+        <v>600</v>
+      </c>
+      <c r="X59" s="3">
         <v>500</v>
       </c>
-      <c r="X59" s="3">
-        <v>700</v>
-      </c>
       <c r="Y59" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="Z59" s="3">
         <v>700</v>
       </c>
       <c r="AA59" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="AB59" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AC59" s="3">
         <v>600</v>
       </c>
       <c r="AD59" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AE59" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="AF59" s="3">
         <v>300</v>
@@ -5945,117 +6219,123 @@
         <v>300</v>
       </c>
       <c r="AH59" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="AI59" s="3">
         <v>300</v>
       </c>
       <c r="AJ59" s="3">
+        <v>600</v>
+      </c>
+      <c r="AK59" s="3">
+        <v>300</v>
+      </c>
+      <c r="AL59" s="3">
         <v>200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F60" s="3">
         <v>1100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>4800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>7500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>7400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>1000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>600</v>
-      </c>
-      <c r="AC60" s="3">
-        <v>700</v>
-      </c>
-      <c r="AD60" s="3">
-        <v>500</v>
       </c>
       <c r="AE60" s="3">
         <v>700</v>
       </c>
       <c r="AF60" s="3">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AG60" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="AH60" s="3">
         <v>900</v>
@@ -6070,13 +6350,19 @@
         <v>600</v>
       </c>
       <c r="AL60" s="3">
+        <v>900</v>
+      </c>
+      <c r="AM60" s="3">
         <v>600</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
+        <v>600</v>
+      </c>
+      <c r="AO60" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -6188,44 +6474,50 @@
       <c r="AM61" s="3">
         <v>0</v>
       </c>
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>17800</v>
+      </c>
+      <c r="F62" s="3">
         <v>500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>2400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>6900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>9700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>13000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>14900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>15600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>18900</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>4</v>
       </c>
@@ -6238,11 +6530,11 @@
       <c r="R62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
-      </c>
-      <c r="T62" s="3">
-        <v>0</v>
+      <c r="S62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U62" s="3">
         <v>0</v>
@@ -6301,8 +6593,14 @@
       <c r="AM62" s="3">
         <v>0</v>
       </c>
+      <c r="AN62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6414,8 +6712,14 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6527,8 +6831,14 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6640,100 +6950,106 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>19400</v>
+      </c>
+      <c r="F66" s="3">
         <v>1500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>3600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>11600</v>
-      </c>
-      <c r="H66" s="3">
-        <v>17200</v>
-      </c>
-      <c r="I66" s="3">
-        <v>20400</v>
       </c>
       <c r="J66" s="3">
         <v>17200</v>
       </c>
       <c r="K66" s="3">
+        <v>20400</v>
+      </c>
+      <c r="L66" s="3">
+        <v>17200</v>
+      </c>
+      <c r="M66" s="3">
         <v>17300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>20400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>900</v>
-      </c>
-      <c r="U66" s="3">
-        <v>700</v>
-      </c>
-      <c r="V66" s="3">
-        <v>600</v>
       </c>
       <c r="W66" s="3">
         <v>700</v>
       </c>
       <c r="X66" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y66" s="3">
+        <v>700</v>
+      </c>
+      <c r="Z66" s="3">
         <v>1200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>600</v>
-      </c>
-      <c r="AC66" s="3">
-        <v>700</v>
-      </c>
-      <c r="AD66" s="3">
-        <v>500</v>
       </c>
       <c r="AE66" s="3">
         <v>700</v>
       </c>
       <c r="AF66" s="3">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AG66" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="AH66" s="3">
         <v>900</v>
@@ -6748,13 +7064,19 @@
         <v>600</v>
       </c>
       <c r="AL66" s="3">
+        <v>900</v>
+      </c>
+      <c r="AM66" s="3">
         <v>600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
+        <v>600</v>
+      </c>
+      <c r="AO66" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6794,8 +7116,10 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6907,8 +7231,14 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7020,16 +7350,22 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E70" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F70" s="3">
         <v>0</v>
@@ -7038,26 +7374,26 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
         <v>5300</v>
       </c>
-      <c r="I70" s="3">
+      <c r="K70" s="3">
         <v>11900</v>
       </c>
-      <c r="J70" s="3">
+      <c r="L70" s="3">
         <v>22800</v>
       </c>
-      <c r="K70" s="3">
+      <c r="M70" s="3">
         <v>24800</v>
       </c>
-      <c r="L70" s="3">
+      <c r="N70" s="3">
         <v>16800</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
@@ -7133,8 +7469,14 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7246,121 +7588,133 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-100700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-93300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-85000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-96700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-93700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-92200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-115600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-117000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-116400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-119500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-116000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-115800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-115100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-113200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-111600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-110200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-109400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-108400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-107400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-106400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-105700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-104700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-103900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-103100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-102200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-101200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-100000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-98900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-98200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-97200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-96000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>-94700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>-92600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>-90800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>-89100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>-88000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>-86700</v>
       </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7472,8 +7826,14 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7585,8 +7945,14 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7698,121 +8064,133 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>35700</v>
+      </c>
+      <c r="F76" s="3">
         <v>43600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>51900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>40300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>43500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>47700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>27600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>31400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>36800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>42700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>72700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>77100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>81000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>86300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>89900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>91300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>92100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>5700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>6700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>7600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>8300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>6200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>5100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>4300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>4500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>5000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>5000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>5400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>5400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>6200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>5800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>5800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>7300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>8700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>8100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>7000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7924,239 +8302,257 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F80" s="2">
         <v>45869</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45777</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45688</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45596</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45504</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45412</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45322</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45230</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45138</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45046</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44957</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44865</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44773</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44681</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44592</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44500</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44408</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44316</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44227</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44135</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44043</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43951</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43861</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43769</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43677</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43585</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43496</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43404</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43312</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43220</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43131</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42947</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42855</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42766</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-8400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>11700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-3000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>23400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>1300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>2800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-3200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-1900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-1400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-800</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-1000</v>
       </c>
       <c r="U81" s="3">
         <v>-1000</v>
       </c>
       <c r="V81" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="W81" s="3">
         <v>-1000</v>
       </c>
       <c r="X81" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="Y81" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="Z81" s="3">
         <v>-900</v>
       </c>
       <c r="AA81" s="3">
-        <v>-1100</v>
+        <v>-800</v>
       </c>
       <c r="AB81" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="AC81" s="3">
         <v>-1100</v>
       </c>
       <c r="AD81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AE81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AF81" s="3">
         <v>-700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8196,8 +8592,10 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8234,11 +8632,11 @@
       <c r="N83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -8309,8 +8707,14 @@
       <c r="AM83" s="3">
         <v>0</v>
       </c>
+      <c r="AN83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8422,8 +8826,14 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8535,8 +8945,14 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8648,8 +9064,14 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8761,8 +9183,14 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8874,121 +9302,133 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-2000</v>
+        <v>-800</v>
       </c>
       <c r="E89" s="3">
         <v>-1000</v>
       </c>
       <c r="F89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H89" s="3">
         <v>-500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-2000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-1900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-1400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-1200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-900</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-600</v>
-      </c>
-      <c r="W89" s="3">
-        <v>-1300</v>
       </c>
       <c r="X89" s="3">
         <v>-600</v>
       </c>
       <c r="Y89" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-600</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>-400</v>
       </c>
       <c r="AA89" s="3">
         <v>-600</v>
       </c>
       <c r="AB89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AC89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>-1600</v>
-      </c>
-      <c r="AJ89" s="3">
-        <v>-900</v>
-      </c>
-      <c r="AK89" s="3">
-        <v>-800</v>
       </c>
       <c r="AL89" s="3">
         <v>-900</v>
       </c>
       <c r="AM89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AN89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AO89" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9028,8 +9468,10 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9066,11 +9508,11 @@
       <c r="N91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -9141,8 +9583,14 @@
       <c r="AM91" s="3">
         <v>0</v>
       </c>
+      <c r="AN91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9254,8 +9702,14 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9367,38 +9821,44 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>4</v>
+      <c r="D94" s="3">
+        <v>5000</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
+        <v>-3000</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-7000</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-5000</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>4</v>
       </c>
@@ -9411,11 +9871,11 @@
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
@@ -9480,8 +9940,14 @@
       <c r="AM94" s="3">
         <v>0</v>
       </c>
+      <c r="AN94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9521,8 +9987,10 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9559,11 +10027,11 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -9634,8 +10102,14 @@
       <c r="AM96" s="3">
         <v>0</v>
       </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9747,8 +10221,14 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9860,8 +10340,14 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9973,121 +10459,133 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>4</v>
+      <c r="D100" s="3">
+        <v>500</v>
       </c>
       <c r="E100" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-3900</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-10700</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-10200</v>
       </c>
       <c r="I100" s="3">
         <v>-10700</v>
       </c>
       <c r="J100" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="K100" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="L100" s="3">
         <v>-7000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>6300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-4300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-3800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-3400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>87400</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>2800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>1800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>1400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>500</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>1400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>900</v>
       </c>
-      <c r="AH100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI100" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ100" s="3">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="AK100" s="3">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="AL100" s="3">
         <v>1800</v>
       </c>
       <c r="AM100" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AN100" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AO100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10199,117 +10697,129 @@
       <c r="AM101" s="3">
         <v>0</v>
       </c>
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-4500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-11800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-17500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-11000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-12200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>6600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-4600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-4300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-5300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>86000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-1200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>1600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>1300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-300</v>
-      </c>
-      <c r="AB102" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AC102" s="3">
-        <v>-200</v>
       </c>
       <c r="AD102" s="3">
         <v>-200</v>
       </c>
       <c r="AE102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AF102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG102" s="3">
         <v>-900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>1000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>-800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PMCB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PMCB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="92">
   <si>
     <t>PMCB</t>
   </si>
@@ -1478,10 +1478,10 @@
         <v>-12800</v>
       </c>
       <c r="H14" s="3">
-        <v>6200</v>
+        <v>3000</v>
       </c>
       <c r="I14" s="3">
-        <v>4300</v>
+        <v>-700</v>
       </c>
       <c r="J14" s="3">
         <v>-22100</v>
@@ -2037,10 +2037,10 @@
         <v>200</v>
       </c>
       <c r="H20" s="3">
-        <v>-3800</v>
+        <v>-600</v>
       </c>
       <c r="I20" s="3">
-        <v>-3500</v>
+        <v>1400</v>
       </c>
       <c r="J20" s="3">
         <v>-2000</v>
@@ -2156,10 +2156,10 @@
         <v>-1300</v>
       </c>
       <c r="H21" s="3">
-        <v>2900</v>
+        <v>-300</v>
       </c>
       <c r="I21" s="3">
-        <v>2400</v>
+        <v>-2500</v>
       </c>
       <c r="J21" s="3">
         <v>800</v>
@@ -2873,7 +2873,7 @@
         <v>-3000</v>
       </c>
       <c r="I27" s="3">
-        <v>-3000</v>
+        <v>-1600</v>
       </c>
       <c r="J27" s="3">
         <v>17200</v>
@@ -3465,10 +3465,10 @@
         <v>-200</v>
       </c>
       <c r="H32" s="3">
-        <v>3800</v>
+        <v>600</v>
       </c>
       <c r="I32" s="3">
-        <v>3500</v>
+        <v>-1400</v>
       </c>
       <c r="J32" s="3">
         <v>2000</v>
@@ -4261,10 +4261,10 @@
         <v>400</v>
       </c>
       <c r="E42" s="3">
-        <v>5200</v>
+        <v>200</v>
       </c>
       <c r="F42" s="3">
-        <v>4900</v>
+        <v>300</v>
       </c>
       <c r="G42" s="3">
         <v>400</v>
@@ -4379,11 +4379,11 @@
       <c r="D43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
+      <c r="E43" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F43" s="3">
+        <v>4600</v>
       </c>
       <c r="G43" s="3">
         <v>3700</v>
@@ -6129,7 +6129,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3">
         <v>200</v>
